--- a/sample_data/D_chain_multi_branch.xlsx
+++ b/sample_data/D_chain_multi_branch.xlsx
@@ -525,13 +525,13 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
         <v>36.63</v>
       </c>
       <c r="G2" t="n">
-        <v>44.69</v>
+        <v>33.7</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>47036</v>
@@ -554,19 +554,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>33.4</v>
+        <v>33.75</v>
       </c>
       <c r="G3" t="n">
-        <v>40.75</v>
+        <v>41.17</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46837</v>
+        <v>46730</v>
       </c>
     </row>
     <row r="4">
@@ -589,16 +589,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>40.78</v>
+        <v>42.87</v>
       </c>
       <c r="G4" t="n">
-        <v>48.94</v>
+        <v>51.44</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46852</v>
+        <v>46822</v>
       </c>
     </row>
     <row r="5">
@@ -618,19 +618,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>49.98</v>
+        <v>53.55</v>
       </c>
       <c r="G5" t="n">
-        <v>58.98</v>
+        <v>63.19</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46720</v>
+        <v>47218</v>
       </c>
     </row>
     <row r="6">
@@ -650,19 +650,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>445</v>
+        <v>243</v>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>29.08</v>
+        <v>28.39</v>
       </c>
       <c r="G6" t="n">
-        <v>36.35</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>46680</v>
+        <v>35.49</v>
       </c>
     </row>
     <row r="7">
@@ -682,19 +679,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F7" t="n">
-        <v>32.56</v>
+        <v>32.47</v>
       </c>
       <c r="G7" t="n">
-        <v>29.96</v>
+        <v>39.29</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46306</v>
+        <v>47193</v>
       </c>
     </row>
     <row r="8">
@@ -714,19 +711,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>123.53</v>
+        <v>112.76</v>
       </c>
       <c r="G8" t="n">
-        <v>142.06</v>
+        <v>129.67</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>47206</v>
+        <v>46987</v>
       </c>
     </row>
     <row r="9">
@@ -746,19 +743,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="F9" t="n">
-        <v>93.59999999999999</v>
+        <v>96.47</v>
       </c>
       <c r="G9" t="n">
-        <v>107.64</v>
+        <v>110.94</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46549</v>
+        <v>46678</v>
       </c>
     </row>
     <row r="10">
@@ -781,16 +778,16 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>109.23</v>
+        <v>106.57</v>
       </c>
       <c r="G10" t="n">
-        <v>127.8</v>
+        <v>124.69</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46529</v>
+        <v>46874</v>
       </c>
     </row>
     <row r="11">
@@ -810,19 +807,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>23.08</v>
+        <v>24.2</v>
       </c>
       <c r="G11" t="n">
-        <v>28.85</v>
+        <v>30.25</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>47192</v>
+        <v>46616</v>
       </c>
     </row>
     <row r="12">
@@ -845,16 +842,16 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>77.16</v>
+        <v>72.3</v>
       </c>
       <c r="G12" t="n">
-        <v>89.51000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46759</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="13">
@@ -877,16 +874,16 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>170.88</v>
+        <v>162.17</v>
       </c>
       <c r="G13" t="n">
-        <v>194.8</v>
+        <v>184.87</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46720</v>
+        <v>46761</v>
       </c>
     </row>
     <row r="14">
@@ -906,19 +903,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>85.83</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>99.56</v>
+        <v>100.13</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46620</v>
+        <v>46675</v>
       </c>
     </row>
     <row r="15">
@@ -938,19 +935,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
-        <v>65.34999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="G15" t="n">
-        <v>77.11</v>
+        <v>76.33</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46602</v>
+        <v>46760</v>
       </c>
     </row>
     <row r="16">
@@ -970,19 +967,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F16" t="n">
-        <v>79.8</v>
+        <v>78.83</v>
       </c>
       <c r="G16" t="n">
-        <v>94.16</v>
+        <v>93.02</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46705</v>
+        <v>46394</v>
       </c>
     </row>
     <row r="17">
@@ -1002,19 +999,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>97.08</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>112.61</v>
+        <v>114.25</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>47090</v>
+        <v>47134</v>
       </c>
     </row>
     <row r="18">
@@ -1034,19 +1031,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="E18" t="n">
-        <v>302</v>
+        <v>32</v>
       </c>
       <c r="F18" t="n">
-        <v>187.65</v>
+        <v>188.31</v>
       </c>
       <c r="G18" t="n">
-        <v>212.04</v>
+        <v>212.79</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46572</v>
+        <v>46829</v>
       </c>
     </row>
     <row r="19">
@@ -1066,19 +1063,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F19" t="n">
-        <v>207.5</v>
+        <v>215.09</v>
       </c>
       <c r="G19" t="n">
-        <v>232.4</v>
+        <v>240.9</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46798</v>
+        <v>46905</v>
       </c>
     </row>
     <row r="20">
@@ -1098,19 +1095,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>486</v>
+        <v>296</v>
       </c>
       <c r="E20" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="F20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>11.96</v>
+        <v>12.19</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>47200</v>
+        <v>46606</v>
       </c>
     </row>
     <row r="21">
@@ -1130,19 +1127,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E21" t="n">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>238.41</v>
+        <v>255.79</v>
       </c>
       <c r="G21" t="n">
-        <v>264.64</v>
+        <v>283.93</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46351</v>
+        <v>46764</v>
       </c>
     </row>
     <row r="22">
@@ -1162,19 +1159,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
-        <v>44.5</v>
+        <v>48.1</v>
       </c>
       <c r="G22" t="n">
-        <v>53.4</v>
+        <v>57.72</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>47120</v>
+        <v>47130</v>
       </c>
     </row>
     <row r="23">
@@ -1197,16 +1194,16 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F23" t="n">
-        <v>59.8</v>
+        <v>55.62</v>
       </c>
       <c r="G23" t="n">
-        <v>71.16</v>
+        <v>66.19</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>47193</v>
+        <v>47049</v>
       </c>
     </row>
     <row r="24">
@@ -1229,16 +1226,16 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>69.11</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>81.55</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46320</v>
+        <v>46789</v>
       </c>
     </row>
     <row r="25">
@@ -1261,16 +1258,16 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F25" t="n">
-        <v>399.5</v>
+        <v>401.78</v>
       </c>
       <c r="G25" t="n">
-        <v>439.45</v>
+        <v>441.96</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46586</v>
+        <v>46569</v>
       </c>
     </row>
     <row r="26">
@@ -1290,19 +1287,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="F26" t="n">
-        <v>297.04</v>
+        <v>303</v>
       </c>
       <c r="G26" t="n">
-        <v>329.71</v>
+        <v>336.33</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46656</v>
+        <v>46394</v>
       </c>
     </row>
     <row r="27">
@@ -1322,19 +1319,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E27" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>519.4299999999999</v>
+        <v>527.0599999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>560.98</v>
+        <v>569.22</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46622</v>
+        <v>46354</v>
       </c>
     </row>
     <row r="28">
@@ -1354,19 +1351,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F28" t="n">
-        <v>169.41</v>
+        <v>158.06</v>
       </c>
       <c r="G28" t="n">
-        <v>186.35</v>
+        <v>173.87</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46836</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="29">
@@ -1386,19 +1383,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>134.79</v>
+        <v>134.23</v>
       </c>
       <c r="G29" t="n">
-        <v>156.36</v>
+        <v>155.71</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46346</v>
+        <v>46292</v>
       </c>
     </row>
     <row r="30">
@@ -1418,19 +1415,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="E30" t="n">
-        <v>160</v>
+        <v>61</v>
       </c>
       <c r="F30" t="n">
-        <v>108.76</v>
+        <v>107.23</v>
       </c>
       <c r="G30" t="n">
-        <v>127.25</v>
+        <v>125.46</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>47040</v>
+        <v>46670</v>
       </c>
     </row>
     <row r="31">
@@ -1450,19 +1447,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>39</v>
+        <v>161</v>
       </c>
       <c r="E31" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F31" t="n">
-        <v>29.64</v>
+        <v>30.86</v>
       </c>
       <c r="G31" t="n">
-        <v>36.75</v>
+        <v>38.27</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>47033</v>
+        <v>46390</v>
       </c>
     </row>
     <row r="32">
@@ -1485,16 +1482,16 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F32" t="n">
-        <v>38.98</v>
+        <v>37.44</v>
       </c>
       <c r="G32" t="n">
-        <v>47.56</v>
+        <v>45.68</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46393</v>
+        <v>47163</v>
       </c>
     </row>
     <row r="33">
@@ -1514,19 +1511,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F33" t="n">
-        <v>73.56999999999999</v>
+        <v>71.16</v>
       </c>
       <c r="G33" t="n">
-        <v>88.28</v>
+        <v>85.39</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>47114</v>
+        <v>46587</v>
       </c>
     </row>
     <row r="34">
@@ -1546,19 +1543,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E34" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="F34" t="n">
-        <v>35.47</v>
+        <v>37.61</v>
       </c>
       <c r="G34" t="n">
-        <v>43.27</v>
+        <v>45.88</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46312</v>
+        <v>46389</v>
       </c>
     </row>
     <row r="35">
@@ -1578,19 +1575,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>173</v>
+        <v>46</v>
       </c>
       <c r="E35" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F35" t="n">
-        <v>42.14</v>
+        <v>43.69</v>
       </c>
       <c r="G35" t="n">
-        <v>50.99</v>
+        <v>52.86</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>47160</v>
+        <v>46685</v>
       </c>
     </row>
     <row r="36">
@@ -1610,19 +1607,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="E36" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="F36" t="n">
-        <v>48.78</v>
+        <v>49.3</v>
       </c>
       <c r="G36" t="n">
-        <v>59.02</v>
+        <v>59.65</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46747</v>
+        <v>46681</v>
       </c>
     </row>
     <row r="37">
@@ -1642,19 +1639,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="E37" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F37" t="n">
-        <v>55.14</v>
+        <v>57.29</v>
       </c>
       <c r="G37" t="n">
-        <v>66.17</v>
+        <v>68.75</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46765</v>
+        <v>46668</v>
       </c>
     </row>
     <row r="38">
@@ -1677,16 +1674,16 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F38" t="n">
-        <v>89.83</v>
+        <v>88.25</v>
       </c>
       <c r="G38" t="n">
-        <v>106</v>
+        <v>104.13</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46350</v>
+        <v>46557</v>
       </c>
     </row>
     <row r="39">
@@ -1706,19 +1703,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>302</v>
+        <v>91</v>
       </c>
       <c r="E39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>66.01000000000001</v>
+        <v>64.86</v>
       </c>
       <c r="G39" t="n">
-        <v>78.55</v>
-      </c>
-      <c r="H39" s="1" t="n">
-        <v>47059</v>
+        <v>77.18000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1738,19 +1732,19 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>228</v>
+        <v>516</v>
       </c>
       <c r="E40" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="F40" t="n">
-        <v>47.81</v>
+        <v>45.64</v>
       </c>
       <c r="G40" t="n">
-        <v>57.37</v>
+        <v>54.77</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46994</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="41">
@@ -1770,19 +1764,19 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>515</v>
+        <v>312</v>
       </c>
       <c r="E41" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="F41" t="n">
-        <v>417.7</v>
+        <v>433.68</v>
       </c>
       <c r="G41" t="n">
-        <v>455.29</v>
+        <v>472.71</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46875</v>
+        <v>47195</v>
       </c>
     </row>
     <row r="42">
@@ -1802,19 +1796,19 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F42" t="n">
-        <v>148.62</v>
+        <v>162.73</v>
       </c>
       <c r="G42" t="n">
-        <v>169.43</v>
+        <v>185.51</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46292</v>
+        <v>47125</v>
       </c>
     </row>
     <row r="43">
@@ -1837,16 +1831,16 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F43" t="n">
-        <v>29.16</v>
+        <v>28.08</v>
       </c>
       <c r="G43" t="n">
-        <v>36.45</v>
+        <v>35.1</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46716</v>
+        <v>46999</v>
       </c>
     </row>
     <row r="44">
@@ -1869,16 +1863,16 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F44" t="n">
-        <v>25.73</v>
+        <v>25.42</v>
       </c>
       <c r="G44" t="n">
-        <v>32.16</v>
+        <v>31.78</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>47105</v>
+        <v>46854</v>
       </c>
     </row>
     <row r="45">
@@ -1898,19 +1892,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>242</v>
+        <v>144</v>
       </c>
       <c r="E45" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>33.49</v>
+        <v>35.85</v>
       </c>
       <c r="G45" t="n">
-        <v>41.19</v>
-      </c>
-      <c r="H45" s="1" t="n">
-        <v>46728</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="46">
@@ -1930,19 +1921,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F46" t="n">
-        <v>37.3</v>
+        <v>38.57</v>
       </c>
       <c r="G46" t="n">
-        <v>47</v>
+        <v>48.6</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46390</v>
+        <v>46967</v>
       </c>
     </row>
     <row r="47">
@@ -1962,19 +1953,19 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>171</v>
+        <v>97</v>
       </c>
       <c r="E47" t="n">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="F47" t="n">
-        <v>237.51</v>
+        <v>238.01</v>
       </c>
       <c r="G47" t="n">
-        <v>280.26</v>
+        <v>280.85</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46760</v>
+        <v>46832</v>
       </c>
     </row>
     <row r="48">
@@ -1994,19 +1985,19 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E48" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F48" t="n">
-        <v>46.33</v>
+        <v>49.26</v>
       </c>
       <c r="G48" t="n">
-        <v>57.45</v>
+        <v>61.08</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46689</v>
+        <v>46559</v>
       </c>
     </row>
     <row r="49">
@@ -2026,19 +2017,19 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>327</v>
+        <v>266</v>
       </c>
       <c r="E49" t="n">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="F49" t="n">
-        <v>90.34999999999999</v>
+        <v>91.61</v>
       </c>
       <c r="G49" t="n">
-        <v>108.42</v>
+        <v>109.93</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>47106</v>
+        <v>47214</v>
       </c>
     </row>
     <row r="50">
@@ -2058,19 +2049,19 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="E50" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F50" t="n">
-        <v>46.08</v>
+        <v>44.13</v>
       </c>
       <c r="G50" t="n">
-        <v>56.68</v>
+        <v>54.28</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46826</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="51">
@@ -2090,19 +2081,19 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E51" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F51" t="n">
-        <v>131.79</v>
+        <v>141.41</v>
       </c>
       <c r="G51" t="n">
-        <v>156.83</v>
+        <v>168.28</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46807</v>
+        <v>46589</v>
       </c>
     </row>
     <row r="52">
@@ -2122,19 +2113,19 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F52" t="n">
-        <v>152.05</v>
+        <v>166.21</v>
       </c>
       <c r="G52" t="n">
-        <v>183.98</v>
+        <v>201.11</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>47155</v>
+        <v>46353</v>
       </c>
     </row>
     <row r="53">
@@ -2154,19 +2145,19 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="E53" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F53" t="n">
-        <v>66.64</v>
+        <v>69.8</v>
       </c>
       <c r="G53" t="n">
-        <v>81.3</v>
+        <v>85.16</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46549</v>
+        <v>46869</v>
       </c>
     </row>
     <row r="54">
@@ -2189,16 +2180,16 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F54" t="n">
-        <v>56.17</v>
+        <v>61.8</v>
       </c>
       <c r="G54" t="n">
-        <v>67.97</v>
+        <v>74.78</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46301</v>
+        <v>46974</v>
       </c>
     </row>
     <row r="55">
@@ -2218,19 +2209,19 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E55" t="n">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="F55" t="n">
-        <v>22.36</v>
+        <v>21.48</v>
       </c>
       <c r="G55" t="n">
-        <v>28.4</v>
+        <v>27.28</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46355</v>
+        <v>46391</v>
       </c>
     </row>
     <row r="56">
@@ -2250,19 +2241,19 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
-        <v>31.4</v>
+        <v>33.24</v>
       </c>
       <c r="G56" t="n">
-        <v>38.94</v>
+        <v>41.22</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46359</v>
+        <v>46643</v>
       </c>
     </row>
     <row r="57">
@@ -2282,16 +2273,16 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>345</v>
+        <v>315</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>666.09</v>
+        <v>628.04</v>
       </c>
       <c r="G57" t="n">
-        <v>785.99</v>
+        <v>741.09</v>
       </c>
     </row>
     <row r="58">
@@ -2311,19 +2302,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>471</v>
+        <v>203</v>
       </c>
       <c r="E58" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>991.08</v>
+        <v>932.09</v>
       </c>
       <c r="G58" t="n">
-        <v>1149.65</v>
-      </c>
-      <c r="H58" s="1" t="n">
-        <v>47083</v>
+        <v>1081.22</v>
       </c>
     </row>
     <row r="59">
@@ -2343,19 +2331,19 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="E59" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F59" t="n">
-        <v>564.14</v>
+        <v>540.52</v>
       </c>
       <c r="G59" t="n">
-        <v>660.04</v>
+        <v>632.41</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46579</v>
+        <v>46957</v>
       </c>
     </row>
     <row r="60">
@@ -2375,19 +2363,19 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="E60" t="n">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F60" t="n">
-        <v>718.08</v>
+        <v>701.4400000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>840.15</v>
+        <v>820.6799999999999</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46549</v>
+        <v>46685</v>
       </c>
     </row>
     <row r="61">
@@ -2407,19 +2395,19 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F61" t="n">
-        <v>91.16</v>
+        <v>92.62</v>
       </c>
       <c r="G61" t="n">
-        <v>109.39</v>
+        <v>111.14</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>47124</v>
+        <v>46557</v>
       </c>
     </row>
     <row r="62">
@@ -2439,19 +2427,19 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="E62" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F62" t="n">
-        <v>125.21</v>
+        <v>125.32</v>
       </c>
       <c r="G62" t="n">
-        <v>149</v>
+        <v>149.13</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46899</v>
+        <v>46749</v>
       </c>
     </row>
     <row r="63">
@@ -2471,19 +2459,19 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="E63" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="F63" t="n">
-        <v>402.56</v>
+        <v>422.13</v>
       </c>
       <c r="G63" t="n">
-        <v>430.74</v>
+        <v>409.47</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46680</v>
+        <v>46354</v>
       </c>
     </row>
     <row r="64">
@@ -2503,19 +2491,19 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>325</v>
+        <v>255</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
-        <v>218.86</v>
+        <v>218.6</v>
       </c>
       <c r="G64" t="n">
-        <v>212.29</v>
+        <v>231.72</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46828</v>
+        <v>46823</v>
       </c>
     </row>
     <row r="65">
@@ -2535,19 +2523,19 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E65" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F65" t="n">
-        <v>265.81</v>
+        <v>258.78</v>
       </c>
       <c r="G65" t="n">
-        <v>281.76</v>
+        <v>274.31</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46368</v>
+        <v>47022</v>
       </c>
     </row>
     <row r="66">
@@ -2570,16 +2558,16 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F66" t="n">
-        <v>138.39</v>
+        <v>149.67</v>
       </c>
       <c r="G66" t="n">
-        <v>166.07</v>
+        <v>179.6</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46688</v>
+        <v>47018</v>
       </c>
     </row>
     <row r="67">
@@ -2599,19 +2587,19 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E67" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F67" t="n">
-        <v>51.95</v>
+        <v>54.2</v>
       </c>
       <c r="G67" t="n">
-        <v>63.9</v>
+        <v>66.67</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46996</v>
+        <v>46937</v>
       </c>
     </row>
     <row r="68">
@@ -2631,19 +2619,19 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E68" t="n">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="F68" t="n">
-        <v>23.62</v>
+        <v>23.99</v>
       </c>
       <c r="G68" t="n">
-        <v>29.76</v>
+        <v>30.23</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>47047</v>
+        <v>47001</v>
       </c>
     </row>
     <row r="69">
@@ -2663,19 +2651,16 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>529</v>
+        <v>136</v>
       </c>
       <c r="E69" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>25.92</v>
+        <v>26.69</v>
       </c>
       <c r="G69" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="H69" s="1" t="n">
-        <v>46680</v>
+        <v>33.36</v>
       </c>
     </row>
     <row r="70">
@@ -2695,19 +2680,19 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="E70" t="n">
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="F70" t="n">
-        <v>20.81</v>
+        <v>21.89</v>
       </c>
       <c r="G70" t="n">
-        <v>26.22</v>
+        <v>27.58</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46705</v>
+        <v>47017</v>
       </c>
     </row>
     <row r="71">
@@ -2727,16 +2712,16 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>480</v>
+        <v>193</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>28.91</v>
+        <v>30.06</v>
       </c>
       <c r="G71" t="n">
-        <v>35.85</v>
+        <v>37.27</v>
       </c>
     </row>
     <row r="72">
@@ -2759,16 +2744,16 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F72" t="n">
-        <v>167.39</v>
+        <v>170.09</v>
       </c>
       <c r="G72" t="n">
-        <v>190.82</v>
+        <v>193.9</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46615</v>
+        <v>46906</v>
       </c>
     </row>
     <row r="73">
@@ -2788,19 +2773,19 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
-        <v>361.77</v>
+        <v>347.52</v>
       </c>
       <c r="G73" t="n">
-        <v>416.04</v>
+        <v>399.65</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>46705</v>
+        <v>46594</v>
       </c>
     </row>
     <row r="74">
@@ -2823,16 +2808,16 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>228.32</v>
+        <v>235.19</v>
       </c>
       <c r="G74" t="n">
-        <v>264.85</v>
+        <v>272.82</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>46778</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="75">
@@ -2852,19 +2837,19 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E75" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
-        <v>303.51</v>
+        <v>297.49</v>
       </c>
       <c r="G75" t="n">
-        <v>339.93</v>
+        <v>333.19</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>47093</v>
+        <v>46883</v>
       </c>
     </row>
     <row r="76">
@@ -2887,16 +2872,16 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F76" t="n">
-        <v>60.99</v>
+        <v>64.87</v>
       </c>
       <c r="G76" t="n">
-        <v>73.19</v>
+        <v>77.84</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46703</v>
+        <v>47218</v>
       </c>
     </row>
     <row r="77">
@@ -2916,19 +2901,19 @@
         </is>
       </c>
       <c r="D77" t="n">
+        <v>14</v>
+      </c>
+      <c r="E77" t="n">
         <v>13</v>
       </c>
-      <c r="E77" t="n">
-        <v>61</v>
-      </c>
       <c r="F77" t="n">
-        <v>99.66</v>
+        <v>96.38</v>
       </c>
       <c r="G77" t="n">
-        <v>118.6</v>
+        <v>114.69</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46964</v>
+        <v>46862</v>
       </c>
     </row>
     <row r="78">
@@ -2948,19 +2933,19 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E78" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F78" t="n">
-        <v>394.81</v>
+        <v>388.05</v>
       </c>
       <c r="G78" t="n">
-        <v>442.19</v>
+        <v>434.62</v>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46769</v>
+        <v>46936</v>
       </c>
     </row>
     <row r="79">
@@ -2980,19 +2965,19 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="E79" t="n">
-        <v>7</v>
+        <v>210</v>
       </c>
       <c r="F79" t="n">
-        <v>1702.41</v>
+        <v>1717.57</v>
       </c>
       <c r="G79" t="n">
-        <v>1872.65</v>
+        <v>1889.33</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46810</v>
+        <v>47121</v>
       </c>
     </row>
     <row r="80">
@@ -3012,19 +2997,19 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="E80" t="n">
-        <v>23</v>
+        <v>428</v>
       </c>
       <c r="F80" t="n">
-        <v>83.23</v>
+        <v>84.02</v>
       </c>
       <c r="G80" t="n">
-        <v>108.2</v>
+        <v>109.23</v>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46931</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="81">
@@ -3044,19 +3029,19 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E81" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F81" t="n">
-        <v>59.37</v>
+        <v>59.87</v>
       </c>
       <c r="G81" t="n">
-        <v>80.15000000000001</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46711</v>
+        <v>46779</v>
       </c>
     </row>
     <row r="82">
@@ -3079,13 +3064,13 @@
         <v>11</v>
       </c>
       <c r="E82" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F82" t="n">
         <v>38.13</v>
       </c>
       <c r="G82" t="n">
-        <v>46.52</v>
+        <v>35.08</v>
       </c>
       <c r="H82" s="1" t="n">
         <v>46760</v>
@@ -3108,7 +3093,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
         <v>8</v>
@@ -3120,7 +3105,7 @@
         <v>39.7</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>46635</v>
+        <v>46974</v>
       </c>
     </row>
     <row r="84">
@@ -3140,19 +3125,19 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="E84" t="n">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="F84" t="n">
-        <v>39.59</v>
+        <v>41.83</v>
       </c>
       <c r="G84" t="n">
-        <v>47.51</v>
+        <v>50.2</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>47059</v>
+        <v>46998</v>
       </c>
     </row>
     <row r="85">
@@ -3172,19 +3157,19 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E85" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F85" t="n">
-        <v>50.64</v>
+        <v>51.1</v>
       </c>
       <c r="G85" t="n">
-        <v>59.76</v>
+        <v>60.3</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>47192</v>
+        <v>46961</v>
       </c>
     </row>
     <row r="86">
@@ -3204,19 +3189,19 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="E86" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="F86" t="n">
-        <v>27.9</v>
+        <v>28.14</v>
       </c>
       <c r="G86" t="n">
-        <v>34.88</v>
+        <v>35.17</v>
       </c>
       <c r="H86" s="1" t="n">
-        <v>47201</v>
+        <v>47045</v>
       </c>
     </row>
     <row r="87">
@@ -3236,19 +3221,19 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E87" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F87" t="n">
-        <v>31.84</v>
+        <v>33.75</v>
       </c>
       <c r="G87" t="n">
-        <v>29.29</v>
+        <v>40.84</v>
       </c>
       <c r="H87" s="1" t="n">
-        <v>47161</v>
+        <v>46560</v>
       </c>
     </row>
     <row r="88">
@@ -3268,16 +3253,19 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>520</v>
+        <v>213</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F88" t="n">
-        <v>119.51</v>
+        <v>120.74</v>
       </c>
       <c r="G88" t="n">
-        <v>137.44</v>
+        <v>138.85</v>
+      </c>
+      <c r="H88" s="1" t="n">
+        <v>47006</v>
       </c>
     </row>
     <row r="89">
@@ -3297,19 +3285,19 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E89" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F89" t="n">
-        <v>96.56999999999999</v>
+        <v>90.19</v>
       </c>
       <c r="G89" t="n">
-        <v>111.06</v>
+        <v>103.72</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>47035</v>
+        <v>46917</v>
       </c>
     </row>
     <row r="90">
@@ -3329,19 +3317,19 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E90" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F90" t="n">
-        <v>104.55</v>
+        <v>104.15</v>
       </c>
       <c r="G90" t="n">
-        <v>122.32</v>
+        <v>121.86</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>47223</v>
+        <v>46849</v>
       </c>
     </row>
     <row r="91">
@@ -3361,19 +3349,19 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="E91" t="n">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="F91" t="n">
-        <v>24.46</v>
+        <v>24.04</v>
       </c>
       <c r="G91" t="n">
-        <v>30.58</v>
+        <v>30.05</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>46542</v>
+        <v>46378</v>
       </c>
     </row>
     <row r="92">
@@ -3393,19 +3381,19 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>333</v>
       </c>
       <c r="F92" t="n">
-        <v>76.70999999999999</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="G92" t="n">
-        <v>88.98</v>
+        <v>92.39</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>46933</v>
+        <v>46749</v>
       </c>
     </row>
     <row r="93">
@@ -3428,16 +3416,16 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F93" t="n">
-        <v>172.08</v>
+        <v>157.5</v>
       </c>
       <c r="G93" t="n">
-        <v>196.17</v>
+        <v>179.55</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>47079</v>
+        <v>47009</v>
       </c>
     </row>
     <row r="94">
@@ -3457,19 +3445,19 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E94" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F94" t="n">
-        <v>90.56</v>
+        <v>90.37</v>
       </c>
       <c r="G94" t="n">
-        <v>105.05</v>
+        <v>104.83</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>46596</v>
+        <v>46855</v>
       </c>
     </row>
     <row r="95">
@@ -3489,19 +3477,19 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E95" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F95" t="n">
-        <v>65.89</v>
+        <v>63.24</v>
       </c>
       <c r="G95" t="n">
-        <v>77.75</v>
+        <v>74.62</v>
       </c>
       <c r="H95" s="1" t="n">
-        <v>46825</v>
+        <v>47192</v>
       </c>
     </row>
     <row r="96">
@@ -3521,19 +3509,19 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="E96" t="n">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="F96" t="n">
-        <v>82.84</v>
+        <v>76.13</v>
       </c>
       <c r="G96" t="n">
-        <v>97.75</v>
+        <v>89.83</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>46342</v>
+        <v>47076</v>
       </c>
     </row>
     <row r="97">
@@ -3553,19 +3541,19 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E97" t="n">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="F97" t="n">
-        <v>101.4</v>
+        <v>97.64</v>
       </c>
       <c r="G97" t="n">
-        <v>117.62</v>
+        <v>113.26</v>
       </c>
       <c r="H97" s="1" t="n">
-        <v>46296</v>
+        <v>46623</v>
       </c>
     </row>
     <row r="98">
@@ -3585,19 +3573,19 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="E98" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F98" t="n">
-        <v>182.64</v>
+        <v>178.2</v>
       </c>
       <c r="G98" t="n">
-        <v>206.38</v>
+        <v>201.37</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>47202</v>
+        <v>46780</v>
       </c>
     </row>
     <row r="99">
@@ -3617,19 +3605,19 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E99" t="n">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="F99" t="n">
-        <v>203.38</v>
+        <v>214.63</v>
       </c>
       <c r="G99" t="n">
-        <v>227.79</v>
+        <v>240.39</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>46382</v>
+        <v>46353</v>
       </c>
     </row>
     <row r="100">
@@ -3652,16 +3640,16 @@
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F100" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="G100" t="n">
-        <v>11.44</v>
+        <v>11.27</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>46773</v>
+        <v>46791</v>
       </c>
     </row>
     <row r="101">
@@ -3681,19 +3669,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>235</v>
+        <v>324</v>
       </c>
       <c r="E101" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>247.3</v>
+        <v>234.59</v>
       </c>
       <c r="G101" t="n">
-        <v>274.5</v>
-      </c>
-      <c r="H101" s="1" t="n">
-        <v>46387</v>
+        <v>260.39</v>
       </c>
     </row>
     <row r="102">
@@ -3716,16 +3701,16 @@
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F102" t="n">
-        <v>46.26</v>
+        <v>45.81</v>
       </c>
       <c r="G102" t="n">
-        <v>55.51</v>
+        <v>54.97</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>47101</v>
+        <v>46533</v>
       </c>
     </row>
     <row r="103">
@@ -3745,19 +3730,19 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E103" t="n">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="F103" t="n">
-        <v>60.61</v>
+        <v>58.94</v>
       </c>
       <c r="G103" t="n">
-        <v>72.13</v>
+        <v>70.14</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>46828</v>
+        <v>46992</v>
       </c>
     </row>
     <row r="104">
@@ -3777,19 +3762,19 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E104" t="n">
-        <v>281</v>
+        <v>14</v>
       </c>
       <c r="F104" t="n">
-        <v>70</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="G104" t="n">
-        <v>82.59999999999999</v>
+        <v>84.58</v>
       </c>
       <c r="H104" s="1" t="n">
-        <v>46344</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="105">
@@ -3812,16 +3797,16 @@
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F105" t="n">
-        <v>382.89</v>
+        <v>402.55</v>
       </c>
       <c r="G105" t="n">
-        <v>421.18</v>
+        <v>442.81</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>46899</v>
+        <v>46928</v>
       </c>
     </row>
     <row r="106">
@@ -3841,19 +3826,19 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E106" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="F106" t="n">
-        <v>324.22</v>
+        <v>316.72</v>
       </c>
       <c r="G106" t="n">
-        <v>359.88</v>
+        <v>351.56</v>
       </c>
       <c r="H106" s="1" t="n">
-        <v>46352</v>
+        <v>47190</v>
       </c>
     </row>
     <row r="107">
@@ -3873,19 +3858,19 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>34</v>
+        <v>144</v>
       </c>
       <c r="E107" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F107" t="n">
-        <v>522.04</v>
+        <v>494.46</v>
       </c>
       <c r="G107" t="n">
-        <v>563.8</v>
+        <v>534.02</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>46979</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="108">
@@ -3905,19 +3890,19 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="E108" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="F108" t="n">
-        <v>166.04</v>
+        <v>163.53</v>
       </c>
       <c r="G108" t="n">
-        <v>182.64</v>
+        <v>179.88</v>
       </c>
       <c r="H108" s="1" t="n">
-        <v>46973</v>
+        <v>47126</v>
       </c>
     </row>
     <row r="109">
@@ -3937,19 +3922,19 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E109" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="F109" t="n">
-        <v>133.35</v>
+        <v>143.78</v>
       </c>
       <c r="G109" t="n">
-        <v>154.69</v>
+        <v>166.78</v>
       </c>
       <c r="H109" s="1" t="n">
-        <v>46782</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="110">
@@ -3969,19 +3954,19 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="E110" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="F110" t="n">
-        <v>111.84</v>
+        <v>114.47</v>
       </c>
       <c r="G110" t="n">
-        <v>130.85</v>
+        <v>133.93</v>
       </c>
       <c r="H110" s="1" t="n">
-        <v>47087</v>
+        <v>46381</v>
       </c>
     </row>
     <row r="111">
@@ -4001,19 +3986,19 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E111" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F111" t="n">
-        <v>29.71</v>
+        <v>31.62</v>
       </c>
       <c r="G111" t="n">
-        <v>36.84</v>
+        <v>39.21</v>
       </c>
       <c r="H111" s="1" t="n">
-        <v>46384</v>
+        <v>46848</v>
       </c>
     </row>
     <row r="112">
@@ -4033,19 +4018,19 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E112" t="n">
-        <v>54</v>
+        <v>438</v>
       </c>
       <c r="F112" t="n">
-        <v>39.69</v>
+        <v>40.94</v>
       </c>
       <c r="G112" t="n">
-        <v>48.42</v>
+        <v>49.95</v>
       </c>
       <c r="H112" s="1" t="n">
-        <v>47156</v>
+        <v>46944</v>
       </c>
     </row>
     <row r="113">
@@ -4065,19 +4050,19 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="E113" t="n">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="F113" t="n">
-        <v>74.39</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="G113" t="n">
-        <v>89.27</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>46674</v>
+        <v>47131</v>
       </c>
     </row>
     <row r="114">
@@ -4100,16 +4085,16 @@
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F114" t="n">
-        <v>37.16</v>
+        <v>37.73</v>
       </c>
       <c r="G114" t="n">
-        <v>45.34</v>
+        <v>46.03</v>
       </c>
       <c r="H114" s="1" t="n">
-        <v>46697</v>
+        <v>47211</v>
       </c>
     </row>
     <row r="115">
@@ -4129,19 +4114,19 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>228</v>
+        <v>283</v>
       </c>
       <c r="E115" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F115" t="n">
-        <v>42.04</v>
+        <v>44.41</v>
       </c>
       <c r="G115" t="n">
-        <v>50.87</v>
+        <v>53.74</v>
       </c>
       <c r="H115" s="1" t="n">
-        <v>46999</v>
+        <v>47156</v>
       </c>
     </row>
     <row r="116">
@@ -4161,19 +4146,19 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="E116" t="n">
-        <v>36</v>
+        <v>434</v>
       </c>
       <c r="F116" t="n">
-        <v>50.16</v>
+        <v>48.2</v>
       </c>
       <c r="G116" t="n">
-        <v>60.69</v>
+        <v>58.32</v>
       </c>
       <c r="H116" s="1" t="n">
-        <v>47072</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="117">
@@ -4193,19 +4178,19 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="E117" t="n">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="F117" t="n">
-        <v>60.5</v>
+        <v>57.91</v>
       </c>
       <c r="G117" t="n">
-        <v>72.59999999999999</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="H117" s="1" t="n">
-        <v>46759</v>
+        <v>46920</v>
       </c>
     </row>
     <row r="118">
@@ -4225,19 +4210,19 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="E118" t="n">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="F118" t="n">
-        <v>88.25</v>
+        <v>87.61</v>
       </c>
       <c r="G118" t="n">
-        <v>104.13</v>
+        <v>103.38</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>47193</v>
+        <v>46863</v>
       </c>
     </row>
     <row r="119">
@@ -4257,19 +4242,19 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E119" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F119" t="n">
-        <v>63.03</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="G119" t="n">
-        <v>75.01000000000001</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>46662</v>
+        <v>46710</v>
       </c>
     </row>
     <row r="120">
@@ -4289,19 +4274,19 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="E120" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F120" t="n">
-        <v>48.41</v>
+        <v>45.01</v>
       </c>
       <c r="G120" t="n">
-        <v>58.09</v>
+        <v>54.01</v>
       </c>
       <c r="H120" s="1" t="n">
-        <v>46598</v>
+        <v>46891</v>
       </c>
     </row>
     <row r="121">
@@ -4321,19 +4306,19 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>242</v>
+        <v>404</v>
       </c>
       <c r="E121" t="n">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="F121" t="n">
-        <v>424.3</v>
+        <v>406.34</v>
       </c>
       <c r="G121" t="n">
-        <v>462.49</v>
+        <v>442.91</v>
       </c>
       <c r="H121" s="1" t="n">
-        <v>47105</v>
+        <v>46623</v>
       </c>
     </row>
     <row r="122">
@@ -4353,19 +4338,16 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>401</v>
+        <v>137</v>
       </c>
       <c r="E122" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>161.78</v>
+        <v>156.22</v>
       </c>
       <c r="G122" t="n">
-        <v>184.43</v>
-      </c>
-      <c r="H122" s="1" t="n">
-        <v>47124</v>
+        <v>178.09</v>
       </c>
     </row>
     <row r="123">
@@ -4385,19 +4367,19 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E123" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F123" t="n">
-        <v>28.16</v>
+        <v>27.84</v>
       </c>
       <c r="G123" t="n">
-        <v>35.2</v>
+        <v>34.8</v>
       </c>
       <c r="H123" s="1" t="n">
-        <v>47097</v>
+        <v>46924</v>
       </c>
     </row>
     <row r="124">
@@ -4420,16 +4402,16 @@
         <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F124" t="n">
-        <v>24.78</v>
+        <v>27.18</v>
       </c>
       <c r="G124" t="n">
-        <v>30.98</v>
+        <v>33.98</v>
       </c>
       <c r="H124" s="1" t="n">
-        <v>47200</v>
+        <v>47206</v>
       </c>
     </row>
     <row r="125">
@@ -4449,19 +4431,19 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>306</v>
+        <v>513</v>
       </c>
       <c r="E125" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F125" t="n">
-        <v>36.17</v>
+        <v>35.36</v>
       </c>
       <c r="G125" t="n">
-        <v>44.49</v>
+        <v>43.49</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>47040</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="126">
@@ -4481,19 +4463,19 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E126" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="F126" t="n">
-        <v>38.81</v>
+        <v>38.12</v>
       </c>
       <c r="G126" t="n">
-        <v>48.9</v>
+        <v>48.03</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>46618</v>
+        <v>47027</v>
       </c>
     </row>
     <row r="127">
@@ -4513,19 +4495,19 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="E127" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="F127" t="n">
-        <v>235.99</v>
+        <v>241.24</v>
       </c>
       <c r="G127" t="n">
-        <v>278.47</v>
+        <v>284.66</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>46351</v>
+        <v>46743</v>
       </c>
     </row>
     <row r="128">
@@ -4548,16 +4530,16 @@
         <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F128" t="n">
-        <v>46.6</v>
+        <v>47.67</v>
       </c>
       <c r="G128" t="n">
-        <v>57.78</v>
+        <v>59.11</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>46393</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="129">
@@ -4577,19 +4559,19 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E129" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F129" t="n">
-        <v>91.42</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="G129" t="n">
-        <v>109.7</v>
+        <v>117.08</v>
       </c>
       <c r="H129" s="1" t="n">
-        <v>46685</v>
+        <v>46349</v>
       </c>
     </row>
     <row r="130">
@@ -4609,16 +4591,19 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>221</v>
+        <v>521</v>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F130" t="n">
-        <v>44.69</v>
+        <v>44.83</v>
       </c>
       <c r="G130" t="n">
-        <v>54.97</v>
+        <v>55.14</v>
+      </c>
+      <c r="H130" s="1" t="n">
+        <v>46368</v>
       </c>
     </row>
     <row r="131">
@@ -4638,19 +4623,19 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="F131" t="n">
-        <v>138.11</v>
+        <v>130.85</v>
       </c>
       <c r="G131" t="n">
-        <v>164.35</v>
+        <v>155.71</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>46294</v>
+        <v>46547</v>
       </c>
     </row>
     <row r="132">
@@ -4670,19 +4655,19 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>422</v>
+        <v>262</v>
       </c>
       <c r="E132" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F132" t="n">
-        <v>161.59</v>
+        <v>166.59</v>
       </c>
       <c r="G132" t="n">
-        <v>195.52</v>
+        <v>201.57</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>47140</v>
+        <v>46532</v>
       </c>
     </row>
     <row r="133">
@@ -4702,19 +4687,19 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E133" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="F133" t="n">
-        <v>65.68000000000001</v>
+        <v>68.84</v>
       </c>
       <c r="G133" t="n">
-        <v>80.13</v>
+        <v>83.98</v>
       </c>
       <c r="H133" s="1" t="n">
-        <v>46880</v>
+        <v>46956</v>
       </c>
     </row>
     <row r="134">
@@ -4737,16 +4722,16 @@
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F134" t="n">
-        <v>59.33</v>
+        <v>56.42</v>
       </c>
       <c r="G134" t="n">
-        <v>71.79000000000001</v>
+        <v>68.27</v>
       </c>
       <c r="H134" s="1" t="n">
-        <v>46991</v>
+        <v>47147</v>
       </c>
     </row>
     <row r="135">
@@ -4766,19 +4751,19 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>149</v>
+        <v>61</v>
       </c>
       <c r="E135" t="n">
-        <v>56</v>
+        <v>170</v>
       </c>
       <c r="F135" t="n">
-        <v>22.31</v>
+        <v>20.96</v>
       </c>
       <c r="G135" t="n">
-        <v>28.33</v>
+        <v>26.62</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>47202</v>
+        <v>46901</v>
       </c>
     </row>
     <row r="136">
@@ -4801,16 +4786,16 @@
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F136" t="n">
-        <v>31.51</v>
+        <v>32.32</v>
       </c>
       <c r="G136" t="n">
-        <v>39.07</v>
+        <v>40.08</v>
       </c>
       <c r="H136" s="1" t="n">
-        <v>46316</v>
+        <v>46581</v>
       </c>
     </row>
     <row r="137">
@@ -4833,16 +4818,16 @@
         <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F137" t="n">
-        <v>626.77</v>
+        <v>635.6900000000001</v>
       </c>
       <c r="G137" t="n">
-        <v>739.59</v>
+        <v>750.11</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>47010</v>
+        <v>46741</v>
       </c>
     </row>
     <row r="138">
@@ -4862,19 +4847,19 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="E138" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="F138" t="n">
-        <v>955.38</v>
+        <v>1026.84</v>
       </c>
       <c r="G138" t="n">
-        <v>1108.24</v>
+        <v>1191.13</v>
       </c>
       <c r="H138" s="1" t="n">
-        <v>46891</v>
+        <v>46663</v>
       </c>
     </row>
     <row r="139">
@@ -4894,19 +4879,19 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="E139" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="F139" t="n">
-        <v>543.17</v>
+        <v>552.08</v>
       </c>
       <c r="G139" t="n">
-        <v>635.51</v>
+        <v>645.9299999999999</v>
       </c>
       <c r="H139" s="1" t="n">
-        <v>46612</v>
+        <v>47197</v>
       </c>
     </row>
     <row r="140">
@@ -4926,19 +4911,19 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E140" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F140" t="n">
-        <v>685.36</v>
+        <v>742.92</v>
       </c>
       <c r="G140" t="n">
-        <v>801.87</v>
+        <v>869.22</v>
       </c>
       <c r="H140" s="1" t="n">
-        <v>46672</v>
+        <v>46664</v>
       </c>
     </row>
     <row r="141">
@@ -4958,19 +4943,19 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E141" t="n">
-        <v>263</v>
+        <v>48</v>
       </c>
       <c r="F141" t="n">
-        <v>93.43000000000001</v>
+        <v>90.34</v>
       </c>
       <c r="G141" t="n">
-        <v>112.12</v>
+        <v>108.41</v>
       </c>
       <c r="H141" s="1" t="n">
-        <v>46565</v>
+        <v>46778</v>
       </c>
     </row>
     <row r="142">
@@ -4990,19 +4975,19 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E142" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F142" t="n">
-        <v>125.19</v>
+        <v>122.97</v>
       </c>
       <c r="G142" t="n">
-        <v>148.98</v>
+        <v>146.33</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>46338</v>
+        <v>46743</v>
       </c>
     </row>
     <row r="143">
@@ -5022,19 +5007,19 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="E143" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F143" t="n">
-        <v>411.09</v>
+        <v>416.91</v>
       </c>
       <c r="G143" t="n">
-        <v>439.87</v>
+        <v>404.4</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>46810</v>
+        <v>46954</v>
       </c>
     </row>
     <row r="144">
@@ -5057,16 +5042,16 @@
         <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F144" t="n">
-        <v>222.31</v>
+        <v>213.07</v>
       </c>
       <c r="G144" t="n">
-        <v>215.64</v>
+        <v>225.85</v>
       </c>
       <c r="H144" s="1" t="n">
-        <v>46971</v>
+        <v>47139</v>
       </c>
     </row>
     <row r="145">
@@ -5089,16 +5074,16 @@
         <v>0</v>
       </c>
       <c r="E145" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F145" t="n">
-        <v>251.63</v>
+        <v>257.63</v>
       </c>
       <c r="G145" t="n">
-        <v>266.73</v>
+        <v>273.09</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>47099</v>
+        <v>47226</v>
       </c>
     </row>
     <row r="146">
@@ -5121,16 +5106,16 @@
         <v>0</v>
       </c>
       <c r="E146" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F146" t="n">
-        <v>151.1</v>
+        <v>148.52</v>
       </c>
       <c r="G146" t="n">
-        <v>181.32</v>
+        <v>178.22</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>46895</v>
+        <v>46691</v>
       </c>
     </row>
     <row r="147">
@@ -5150,19 +5135,19 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E147" t="n">
-        <v>12</v>
+        <v>196</v>
       </c>
       <c r="F147" t="n">
-        <v>52.14</v>
+        <v>53.16</v>
       </c>
       <c r="G147" t="n">
-        <v>64.13</v>
+        <v>65.39</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>47055</v>
+        <v>46360</v>
       </c>
     </row>
     <row r="148">
@@ -5182,19 +5167,19 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="E148" t="n">
-        <v>3</v>
+        <v>111</v>
       </c>
       <c r="F148" t="n">
-        <v>22.28</v>
+        <v>23.96</v>
       </c>
       <c r="G148" t="n">
-        <v>28.07</v>
+        <v>30.19</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>46369</v>
+        <v>46976</v>
       </c>
     </row>
     <row r="149">
@@ -5220,13 +5205,13 @@
         <v>7</v>
       </c>
       <c r="F149" t="n">
-        <v>26.18</v>
+        <v>26.85</v>
       </c>
       <c r="G149" t="n">
-        <v>32.73</v>
+        <v>33.56</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>46566</v>
+        <v>46934</v>
       </c>
     </row>
     <row r="150">
@@ -5249,16 +5234,16 @@
         <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F150" t="n">
-        <v>20.72</v>
+        <v>20.14</v>
       </c>
       <c r="G150" t="n">
-        <v>26.11</v>
+        <v>25.38</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>46829</v>
+        <v>46740</v>
       </c>
     </row>
     <row r="151">
@@ -5278,19 +5263,16 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="E151" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>27.62</v>
+        <v>29.72</v>
       </c>
       <c r="G151" t="n">
-        <v>34.25</v>
-      </c>
-      <c r="H151" s="1" t="n">
-        <v>46780</v>
+        <v>36.85</v>
       </c>
     </row>
     <row r="152">
@@ -5310,19 +5292,19 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E152" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="F152" t="n">
-        <v>171.65</v>
+        <v>179.21</v>
       </c>
       <c r="G152" t="n">
-        <v>195.68</v>
+        <v>204.3</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>47202</v>
+        <v>46592</v>
       </c>
     </row>
     <row r="153">
@@ -5342,16 +5324,19 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F153" t="n">
-        <v>366.82</v>
+        <v>351.94</v>
       </c>
       <c r="G153" t="n">
-        <v>421.84</v>
+        <v>404.73</v>
+      </c>
+      <c r="H153" s="1" t="n">
+        <v>47080</v>
       </c>
     </row>
     <row r="154">
@@ -5374,16 +5359,16 @@
         <v>0</v>
       </c>
       <c r="E154" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F154" t="n">
-        <v>223.3</v>
+        <v>241.21</v>
       </c>
       <c r="G154" t="n">
-        <v>259.03</v>
+        <v>279.8</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>46291</v>
+        <v>46953</v>
       </c>
     </row>
     <row r="155">
@@ -5403,19 +5388,19 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="E155" t="n">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="F155" t="n">
-        <v>318.2</v>
+        <v>308.52</v>
       </c>
       <c r="G155" t="n">
-        <v>356.38</v>
+        <v>345.54</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>46691</v>
+        <v>46896</v>
       </c>
     </row>
     <row r="156">
@@ -5435,19 +5420,19 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="E156" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="F156" t="n">
-        <v>62.39</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G156" t="n">
-        <v>74.87</v>
+        <v>77.62</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>46719</v>
+        <v>46860</v>
       </c>
     </row>
     <row r="157">
@@ -5467,19 +5452,19 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="E157" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F157" t="n">
-        <v>100.2</v>
+        <v>96.95</v>
       </c>
       <c r="G157" t="n">
-        <v>119.24</v>
+        <v>115.37</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>46344</v>
+        <v>46626</v>
       </c>
     </row>
     <row r="158">
@@ -5499,19 +5484,19 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>51</v>
+        <v>166</v>
       </c>
       <c r="E158" t="n">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="F158" t="n">
-        <v>364.26</v>
+        <v>383.31</v>
       </c>
       <c r="G158" t="n">
-        <v>407.97</v>
+        <v>429.31</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>46347</v>
+        <v>46581</v>
       </c>
     </row>
     <row r="159">
@@ -5531,19 +5516,19 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="E159" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="F159" t="n">
-        <v>1568.13</v>
+        <v>1585.23</v>
       </c>
       <c r="G159" t="n">
-        <v>1724.94</v>
+        <v>1743.75</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>46848</v>
+        <v>46563</v>
       </c>
     </row>
     <row r="160">
@@ -5563,16 +5548,19 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>172</v>
+        <v>398</v>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F160" t="n">
-        <v>83.94</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="G160" t="n">
-        <v>109.12</v>
+        <v>107.26</v>
+      </c>
+      <c r="H160" s="1" t="n">
+        <v>46382</v>
       </c>
     </row>
     <row r="161">
@@ -5592,19 +5580,19 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="E161" t="n">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="F161" t="n">
-        <v>62.01</v>
+        <v>59.44</v>
       </c>
       <c r="G161" t="n">
-        <v>83.70999999999999</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>46857</v>
+        <v>46587</v>
       </c>
     </row>
     <row r="162">
@@ -5656,19 +5644,19 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E163" t="n">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="F163" t="n">
         <v>33.35</v>
       </c>
       <c r="G163" t="n">
-        <v>40.69</v>
+        <v>30.68</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>47194</v>
+        <v>46999</v>
       </c>
     </row>
     <row r="164">
@@ -5688,19 +5676,19 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="E164" t="n">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="F164" t="n">
-        <v>39.2</v>
+        <v>39.21</v>
       </c>
       <c r="G164" t="n">
-        <v>47.04</v>
+        <v>47.05</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>47092</v>
+        <v>46646</v>
       </c>
     </row>
     <row r="165">
@@ -5720,19 +5708,19 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="E165" t="n">
-        <v>241</v>
+        <v>118</v>
       </c>
       <c r="F165" t="n">
-        <v>53.9</v>
+        <v>52.75</v>
       </c>
       <c r="G165" t="n">
-        <v>63.6</v>
+        <v>62.24</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>46848</v>
+        <v>46360</v>
       </c>
     </row>
     <row r="166">
@@ -5752,19 +5740,19 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E166" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F166" t="n">
-        <v>27.05</v>
+        <v>29.32</v>
       </c>
       <c r="G166" t="n">
-        <v>33.81</v>
+        <v>36.65</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>46810</v>
+        <v>47171</v>
       </c>
     </row>
     <row r="167">
@@ -5784,19 +5772,19 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E167" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F167" t="n">
-        <v>34.06</v>
+        <v>32.67</v>
       </c>
       <c r="G167" t="n">
-        <v>31.34</v>
+        <v>39.53</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>46859</v>
+        <v>46915</v>
       </c>
     </row>
     <row r="168">
@@ -5819,16 +5807,16 @@
         <v>0</v>
       </c>
       <c r="E168" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F168" t="n">
-        <v>117.76</v>
+        <v>118.31</v>
       </c>
       <c r="G168" t="n">
-        <v>135.42</v>
+        <v>136.06</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>47078</v>
+        <v>46793</v>
       </c>
     </row>
     <row r="169">
@@ -5851,16 +5839,16 @@
         <v>0</v>
       </c>
       <c r="E169" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F169" t="n">
-        <v>95.47</v>
+        <v>92.33</v>
       </c>
       <c r="G169" t="n">
-        <v>109.79</v>
+        <v>106.18</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>46744</v>
+        <v>46762</v>
       </c>
     </row>
     <row r="170">
@@ -5880,19 +5868,19 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="E170" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="F170" t="n">
-        <v>103.57</v>
+        <v>108.96</v>
       </c>
       <c r="G170" t="n">
-        <v>121.18</v>
+        <v>127.48</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>46353</v>
+        <v>47011</v>
       </c>
     </row>
     <row r="171">
@@ -5915,16 +5903,16 @@
         <v>0</v>
       </c>
       <c r="E171" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F171" t="n">
-        <v>24.06</v>
+        <v>24.37</v>
       </c>
       <c r="G171" t="n">
-        <v>30.07</v>
+        <v>30.46</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>47070</v>
+        <v>46996</v>
       </c>
     </row>
     <row r="172">
@@ -5947,16 +5935,16 @@
         <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F172" t="n">
-        <v>79.37</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="G172" t="n">
-        <v>92.06999999999999</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>46696</v>
+        <v>47148</v>
       </c>
     </row>
     <row r="173">
@@ -5976,19 +5964,19 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>38</v>
+        <v>154</v>
       </c>
       <c r="E173" t="n">
-        <v>13</v>
+        <v>431</v>
       </c>
       <c r="F173" t="n">
-        <v>159.55</v>
+        <v>166.78</v>
       </c>
       <c r="G173" t="n">
-        <v>181.89</v>
+        <v>190.13</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>47108</v>
+        <v>47030</v>
       </c>
     </row>
     <row r="174">
@@ -6008,19 +5996,19 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>48</v>
+        <v>124</v>
       </c>
       <c r="E174" t="n">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="F174" t="n">
-        <v>84.59</v>
+        <v>90.42</v>
       </c>
       <c r="G174" t="n">
-        <v>98.12</v>
+        <v>104.89</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>46956</v>
+        <v>47141</v>
       </c>
     </row>
     <row r="175">
@@ -6043,16 +6031,16 @@
         <v>0</v>
       </c>
       <c r="E175" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F175" t="n">
-        <v>66.5</v>
+        <v>63.88</v>
       </c>
       <c r="G175" t="n">
-        <v>78.47</v>
+        <v>75.38</v>
       </c>
       <c r="H175" s="1" t="n">
-        <v>47156</v>
+        <v>46786</v>
       </c>
     </row>
     <row r="176">
@@ -6072,19 +6060,19 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="E176" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F176" t="n">
-        <v>77.66</v>
+        <v>78.2</v>
       </c>
       <c r="G176" t="n">
-        <v>91.64</v>
+        <v>92.28</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>46397</v>
+        <v>46984</v>
       </c>
     </row>
     <row r="177">
@@ -6104,19 +6092,19 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>435</v>
+        <v>372</v>
       </c>
       <c r="E177" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="F177" t="n">
-        <v>96.79000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G177" t="n">
-        <v>112.28</v>
+        <v>112.06</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>46598</v>
+        <v>47060</v>
       </c>
     </row>
     <row r="178">
@@ -6136,19 +6124,19 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="E178" t="n">
-        <v>8</v>
+        <v>388</v>
       </c>
       <c r="F178" t="n">
-        <v>184.57</v>
+        <v>183.7</v>
       </c>
       <c r="G178" t="n">
-        <v>208.56</v>
+        <v>207.58</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>46644</v>
+        <v>46679</v>
       </c>
     </row>
     <row r="179">
@@ -6171,16 +6159,16 @@
         <v>0</v>
       </c>
       <c r="E179" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="F179" t="n">
-        <v>218.29</v>
+        <v>202.43</v>
       </c>
       <c r="G179" t="n">
-        <v>244.48</v>
+        <v>226.72</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>46374</v>
+        <v>46292</v>
       </c>
     </row>
     <row r="180">
@@ -6200,19 +6188,19 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E180" t="n">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="F180" t="n">
-        <v>8.550000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="G180" t="n">
-        <v>11.12</v>
+        <v>11.73</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>46811</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="181">
@@ -6232,19 +6220,19 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="E181" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="F181" t="n">
-        <v>233.89</v>
+        <v>246.35</v>
       </c>
       <c r="G181" t="n">
-        <v>259.62</v>
+        <v>273.45</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>46733</v>
+        <v>46900</v>
       </c>
     </row>
     <row r="182">
@@ -6264,19 +6252,19 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="E182" t="n">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="F182" t="n">
-        <v>45.12</v>
+        <v>48.17</v>
       </c>
       <c r="G182" t="n">
-        <v>54.14</v>
+        <v>57.8</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>46691</v>
+        <v>47193</v>
       </c>
     </row>
     <row r="183">
@@ -6296,19 +6284,19 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="E183" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="F183" t="n">
-        <v>58.15</v>
+        <v>60.03</v>
       </c>
       <c r="G183" t="n">
-        <v>69.2</v>
+        <v>71.44</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>47092</v>
+        <v>46344</v>
       </c>
     </row>
     <row r="184">
@@ -6328,19 +6316,19 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E184" t="n">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="F184" t="n">
-        <v>70.45</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="G184" t="n">
-        <v>83.13</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>47050</v>
+        <v>47078</v>
       </c>
     </row>
     <row r="185">
@@ -6360,19 +6348,19 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E185" t="n">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="F185" t="n">
-        <v>384.1</v>
+        <v>380.82</v>
       </c>
       <c r="G185" t="n">
-        <v>422.51</v>
+        <v>418.9</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>46928</v>
+        <v>46656</v>
       </c>
     </row>
     <row r="186">
@@ -6395,16 +6383,16 @@
         <v>0</v>
       </c>
       <c r="E186" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F186" t="n">
-        <v>321.47</v>
+        <v>319.43</v>
       </c>
       <c r="G186" t="n">
-        <v>356.83</v>
+        <v>354.57</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>46781</v>
+        <v>46724</v>
       </c>
     </row>
     <row r="187">
@@ -6424,19 +6412,19 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="E187" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F187" t="n">
-        <v>523.08</v>
+        <v>508.85</v>
       </c>
       <c r="G187" t="n">
-        <v>564.9299999999999</v>
+        <v>549.5599999999999</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>46946</v>
+        <v>47214</v>
       </c>
     </row>
     <row r="188">
@@ -6456,19 +6444,19 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="E188" t="n">
-        <v>398</v>
+        <v>10</v>
       </c>
       <c r="F188" t="n">
-        <v>167.04</v>
+        <v>161.88</v>
       </c>
       <c r="G188" t="n">
-        <v>183.74</v>
+        <v>178.07</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>47179</v>
+        <v>46944</v>
       </c>
     </row>
     <row r="189">
@@ -6488,19 +6476,19 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="E189" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="F189" t="n">
-        <v>141.84</v>
+        <v>135.55</v>
       </c>
       <c r="G189" t="n">
-        <v>164.53</v>
+        <v>157.24</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>47187</v>
+        <v>47107</v>
       </c>
     </row>
     <row r="190">
@@ -6520,19 +6508,19 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E190" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="F190" t="n">
-        <v>110.8</v>
+        <v>111.58</v>
       </c>
       <c r="G190" t="n">
-        <v>129.64</v>
+        <v>130.55</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>46976</v>
+        <v>46832</v>
       </c>
     </row>
     <row r="191">
@@ -6552,19 +6540,19 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="E191" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F191" t="n">
-        <v>30.81</v>
+        <v>30.28</v>
       </c>
       <c r="G191" t="n">
-        <v>38.2</v>
+        <v>37.55</v>
       </c>
       <c r="H191" s="1" t="n">
-        <v>46916</v>
+        <v>46760</v>
       </c>
     </row>
     <row r="192">
@@ -6584,19 +6572,19 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>39</v>
+        <v>161</v>
       </c>
       <c r="E192" t="n">
-        <v>25</v>
+        <v>409</v>
       </c>
       <c r="F192" t="n">
-        <v>40.89</v>
+        <v>40.02</v>
       </c>
       <c r="G192" t="n">
-        <v>49.89</v>
+        <v>48.82</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>47198</v>
+        <v>46380</v>
       </c>
     </row>
     <row r="193">
@@ -6616,19 +6604,19 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E193" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="F193" t="n">
-        <v>75.04000000000001</v>
+        <v>75.27</v>
       </c>
       <c r="G193" t="n">
-        <v>90.05</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>47224</v>
+        <v>46629</v>
       </c>
     </row>
     <row r="194">
@@ -6648,19 +6636,19 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="E194" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F194" t="n">
-        <v>36.21</v>
+        <v>36.37</v>
       </c>
       <c r="G194" t="n">
-        <v>44.18</v>
+        <v>44.37</v>
       </c>
       <c r="H194" s="1" t="n">
-        <v>46541</v>
+        <v>46389</v>
       </c>
     </row>
     <row r="195">
@@ -6683,16 +6671,16 @@
         <v>0</v>
       </c>
       <c r="E195" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F195" t="n">
-        <v>44.26</v>
+        <v>46.18</v>
       </c>
       <c r="G195" t="n">
-        <v>53.55</v>
+        <v>55.88</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>47222</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="196">
@@ -6712,19 +6700,19 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="E196" t="n">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c r="F196" t="n">
-        <v>49.46</v>
+        <v>51.24</v>
       </c>
       <c r="G196" t="n">
-        <v>59.85</v>
+        <v>62</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>47220</v>
+        <v>46678</v>
       </c>
     </row>
     <row r="197">
@@ -6744,19 +6732,19 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E197" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F197" t="n">
-        <v>59.91</v>
+        <v>56.23</v>
       </c>
       <c r="G197" t="n">
-        <v>71.89</v>
+        <v>67.48</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>47182</v>
+        <v>46344</v>
       </c>
     </row>
     <row r="198">
@@ -6776,19 +6764,19 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E198" t="n">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="F198" t="n">
-        <v>82.73</v>
+        <v>88.77</v>
       </c>
       <c r="G198" t="n">
-        <v>97.62</v>
+        <v>104.75</v>
       </c>
       <c r="H198" s="1" t="n">
-        <v>46917</v>
+        <v>46550</v>
       </c>
     </row>
     <row r="199">
@@ -6811,16 +6799,16 @@
         <v>0</v>
       </c>
       <c r="E199" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F199" t="n">
-        <v>65.52</v>
+        <v>62.65</v>
       </c>
       <c r="G199" t="n">
-        <v>77.97</v>
+        <v>74.55</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>46777</v>
+        <v>46538</v>
       </c>
     </row>
     <row r="200">
@@ -6840,19 +6828,19 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E200" t="n">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="F200" t="n">
-        <v>46.29</v>
+        <v>45.97</v>
       </c>
       <c r="G200" t="n">
-        <v>55.55</v>
+        <v>55.16</v>
       </c>
       <c r="H200" s="1" t="n">
-        <v>46541</v>
+        <v>46341</v>
       </c>
     </row>
     <row r="201">
@@ -6872,19 +6860,19 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E201" t="n">
-        <v>192</v>
+        <v>12</v>
       </c>
       <c r="F201" t="n">
-        <v>409.1</v>
+        <v>412.3</v>
       </c>
       <c r="G201" t="n">
-        <v>445.92</v>
+        <v>449.41</v>
       </c>
       <c r="H201" s="1" t="n">
-        <v>47161</v>
+        <v>46780</v>
       </c>
     </row>
     <row r="202">
@@ -6904,19 +6892,19 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E202" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F202" t="n">
-        <v>162.55</v>
+        <v>149.96</v>
       </c>
       <c r="G202" t="n">
-        <v>185.31</v>
+        <v>170.95</v>
       </c>
       <c r="H202" s="1" t="n">
-        <v>46767</v>
+        <v>46970</v>
       </c>
     </row>
     <row r="203">
@@ -6936,19 +6924,19 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>133</v>
+        <v>33</v>
       </c>
       <c r="E203" t="n">
         <v>7</v>
       </c>
       <c r="F203" t="n">
-        <v>27.58</v>
+        <v>29.02</v>
       </c>
       <c r="G203" t="n">
-        <v>34.47</v>
+        <v>36.27</v>
       </c>
       <c r="H203" s="1" t="n">
-        <v>46653</v>
+        <v>46557</v>
       </c>
     </row>
     <row r="204">
@@ -6968,19 +6956,19 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="E204" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="F204" t="n">
-        <v>25.13</v>
+        <v>25.69</v>
       </c>
       <c r="G204" t="n">
-        <v>31.41</v>
+        <v>32.11</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>46842</v>
+        <v>47191</v>
       </c>
     </row>
     <row r="205">
@@ -7000,16 +6988,19 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>372</v>
+        <v>431</v>
       </c>
       <c r="E205" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="F205" t="n">
-        <v>36.46</v>
+        <v>34.08</v>
       </c>
       <c r="G205" t="n">
-        <v>44.85</v>
+        <v>41.92</v>
+      </c>
+      <c r="H205" s="1" t="n">
+        <v>46531</v>
       </c>
     </row>
     <row r="206">
@@ -7032,16 +7023,16 @@
         <v>0</v>
       </c>
       <c r="E206" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F206" t="n">
-        <v>37.98</v>
+        <v>39.6</v>
       </c>
       <c r="G206" t="n">
-        <v>47.85</v>
+        <v>49.9</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>46613</v>
+        <v>46918</v>
       </c>
     </row>
     <row r="207">
@@ -7061,19 +7052,19 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E207" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="F207" t="n">
-        <v>242.44</v>
+        <v>248.35</v>
       </c>
       <c r="G207" t="n">
-        <v>286.08</v>
+        <v>293.05</v>
       </c>
       <c r="H207" s="1" t="n">
-        <v>46399</v>
+        <v>46868</v>
       </c>
     </row>
     <row r="208">
@@ -7093,19 +7084,19 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>296</v>
+        <v>345</v>
       </c>
       <c r="E208" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F208" t="n">
-        <v>50.12</v>
+        <v>48.63</v>
       </c>
       <c r="G208" t="n">
-        <v>62.15</v>
+        <v>60.3</v>
       </c>
       <c r="H208" s="1" t="n">
-        <v>46939</v>
+        <v>46359</v>
       </c>
     </row>
     <row r="209">
@@ -7128,16 +7119,16 @@
         <v>0</v>
       </c>
       <c r="E209" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F209" t="n">
-        <v>93.06</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="G209" t="n">
-        <v>111.67</v>
+        <v>114.18</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>46940</v>
+        <v>46784</v>
       </c>
     </row>
     <row r="210">
@@ -7157,19 +7148,19 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>109</v>
+        <v>26</v>
       </c>
       <c r="E210" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F210" t="n">
-        <v>42.57</v>
+        <v>43.77</v>
       </c>
       <c r="G210" t="n">
-        <v>52.36</v>
+        <v>53.84</v>
       </c>
       <c r="H210" s="1" t="n">
-        <v>46806</v>
+        <v>46673</v>
       </c>
     </row>
     <row r="211">
@@ -7189,19 +7180,19 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E211" t="n">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="F211" t="n">
-        <v>141.39</v>
+        <v>131.98</v>
       </c>
       <c r="G211" t="n">
-        <v>168.25</v>
+        <v>157.06</v>
       </c>
       <c r="H211" s="1" t="n">
-        <v>46834</v>
+        <v>46835</v>
       </c>
     </row>
     <row r="212">
@@ -7221,19 +7212,19 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="E212" t="n">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="F212" t="n">
-        <v>155.76</v>
+        <v>167.53</v>
       </c>
       <c r="G212" t="n">
-        <v>188.47</v>
+        <v>202.71</v>
       </c>
       <c r="H212" s="1" t="n">
-        <v>46980</v>
+        <v>46659</v>
       </c>
     </row>
     <row r="213">
@@ -7253,19 +7244,19 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E213" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F213" t="n">
-        <v>69.42</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="G213" t="n">
-        <v>84.69</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H213" s="1" t="n">
-        <v>46735</v>
+        <v>46878</v>
       </c>
     </row>
     <row r="214">
@@ -7285,19 +7276,19 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E214" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F214" t="n">
-        <v>58.21</v>
+        <v>57.81</v>
       </c>
       <c r="G214" t="n">
-        <v>70.43000000000001</v>
+        <v>69.95</v>
       </c>
       <c r="H214" s="1" t="n">
-        <v>46350</v>
+        <v>46613</v>
       </c>
     </row>
     <row r="215">
@@ -7317,16 +7308,19 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>251</v>
+        <v>470</v>
       </c>
       <c r="E215" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="F215" t="n">
-        <v>22.09</v>
+        <v>22.38</v>
       </c>
       <c r="G215" t="n">
-        <v>28.05</v>
+        <v>28.42</v>
+      </c>
+      <c r="H215" s="1" t="n">
+        <v>46584</v>
       </c>
     </row>
     <row r="216">
@@ -7346,19 +7340,19 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="E216" t="n">
-        <v>18</v>
+        <v>259</v>
       </c>
       <c r="F216" t="n">
-        <v>32.49</v>
+        <v>33.06</v>
       </c>
       <c r="G216" t="n">
-        <v>40.29</v>
+        <v>40.99</v>
       </c>
       <c r="H216" s="1" t="n">
-        <v>46714</v>
+        <v>47199</v>
       </c>
     </row>
     <row r="217">
@@ -7378,19 +7372,19 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E217" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="F217" t="n">
-        <v>650.3</v>
+        <v>642.71</v>
       </c>
       <c r="G217" t="n">
-        <v>767.35</v>
+        <v>758.4</v>
       </c>
       <c r="H217" s="1" t="n">
-        <v>46856</v>
+        <v>46919</v>
       </c>
     </row>
     <row r="218">
@@ -7410,19 +7404,19 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="E218" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F218" t="n">
-        <v>958.3200000000001</v>
+        <v>973.0700000000001</v>
       </c>
       <c r="G218" t="n">
-        <v>1111.65</v>
+        <v>1128.76</v>
       </c>
       <c r="H218" s="1" t="n">
-        <v>47141</v>
+        <v>46766</v>
       </c>
     </row>
     <row r="219">
@@ -7442,19 +7436,16 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>227</v>
+        <v>364</v>
       </c>
       <c r="E219" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="F219" t="n">
-        <v>536.03</v>
+        <v>518.67</v>
       </c>
       <c r="G219" t="n">
-        <v>627.16</v>
-      </c>
-      <c r="H219" s="1" t="n">
-        <v>47036</v>
+        <v>606.84</v>
       </c>
     </row>
     <row r="220">
@@ -7474,19 +7465,16 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>410</v>
+        <v>363</v>
       </c>
       <c r="E220" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F220" t="n">
-        <v>721.1799999999999</v>
+        <v>708.67</v>
       </c>
       <c r="G220" t="n">
-        <v>843.78</v>
-      </c>
-      <c r="H220" s="1" t="n">
-        <v>46682</v>
+        <v>829.14</v>
       </c>
     </row>
     <row r="221">
@@ -7506,19 +7494,19 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E221" t="n">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="F221" t="n">
-        <v>95.8</v>
+        <v>95</v>
       </c>
       <c r="G221" t="n">
-        <v>114.96</v>
+        <v>114</v>
       </c>
       <c r="H221" s="1" t="n">
-        <v>46304</v>
+        <v>46972</v>
       </c>
     </row>
     <row r="222">
@@ -7538,19 +7526,19 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="E222" t="n">
-        <v>308</v>
+        <v>7</v>
       </c>
       <c r="F222" t="n">
-        <v>122.35</v>
+        <v>118.01</v>
       </c>
       <c r="G222" t="n">
-        <v>145.6</v>
+        <v>140.43</v>
       </c>
       <c r="H222" s="1" t="n">
-        <v>46787</v>
+        <v>47040</v>
       </c>
     </row>
     <row r="223">
@@ -7573,16 +7561,16 @@
         <v>0</v>
       </c>
       <c r="E223" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F223" t="n">
-        <v>398.24</v>
+        <v>413.7</v>
       </c>
       <c r="G223" t="n">
-        <v>426.12</v>
+        <v>442.66</v>
       </c>
       <c r="H223" s="1" t="n">
-        <v>46634</v>
+        <v>46782</v>
       </c>
     </row>
     <row r="224">
@@ -7602,19 +7590,19 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="E224" t="n">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="F224" t="n">
-        <v>217.79</v>
+        <v>213.98</v>
       </c>
       <c r="G224" t="n">
-        <v>211.26</v>
+        <v>207.56</v>
       </c>
       <c r="H224" s="1" t="n">
-        <v>46807</v>
+        <v>47038</v>
       </c>
     </row>
     <row r="225">
@@ -7634,19 +7622,19 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="E225" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="F225" t="n">
-        <v>260.37</v>
+        <v>251.98</v>
       </c>
       <c r="G225" t="n">
-        <v>275.99</v>
+        <v>267.1</v>
       </c>
       <c r="H225" s="1" t="n">
-        <v>46936</v>
+        <v>46972</v>
       </c>
     </row>
     <row r="226">
@@ -7666,16 +7654,16 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>527</v>
+        <v>366</v>
       </c>
       <c r="E226" t="n">
         <v>0</v>
       </c>
       <c r="F226" t="n">
-        <v>139.53</v>
+        <v>142.29</v>
       </c>
       <c r="G226" t="n">
-        <v>167.44</v>
+        <v>170.75</v>
       </c>
     </row>
     <row r="227">
@@ -7695,19 +7683,19 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="E227" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="F227" t="n">
-        <v>53.43</v>
+        <v>52.23</v>
       </c>
       <c r="G227" t="n">
-        <v>65.72</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="H227" s="1" t="n">
-        <v>46971</v>
+        <v>46896</v>
       </c>
     </row>
     <row r="228">
@@ -7727,19 +7715,19 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E228" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F228" t="n">
-        <v>23.17</v>
+        <v>22.72</v>
       </c>
       <c r="G228" t="n">
-        <v>29.19</v>
+        <v>28.63</v>
       </c>
       <c r="H228" s="1" t="n">
-        <v>46369</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="229">
@@ -7762,16 +7750,16 @@
         <v>0</v>
       </c>
       <c r="E229" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F229" t="n">
-        <v>27.34</v>
+        <v>27.35</v>
       </c>
       <c r="G229" t="n">
-        <v>34.17</v>
+        <v>34.19</v>
       </c>
       <c r="H229" s="1" t="n">
-        <v>46849</v>
+        <v>46883</v>
       </c>
     </row>
     <row r="230">
@@ -7794,16 +7782,16 @@
         <v>0</v>
       </c>
       <c r="E230" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F230" t="n">
-        <v>20.97</v>
+        <v>21.3</v>
       </c>
       <c r="G230" t="n">
-        <v>26.42</v>
+        <v>26.84</v>
       </c>
       <c r="H230" s="1" t="n">
-        <v>46742</v>
+        <v>47149</v>
       </c>
     </row>
     <row r="231">
@@ -7823,19 +7811,19 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E231" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F231" t="n">
-        <v>29.85</v>
+        <v>28.07</v>
       </c>
       <c r="G231" t="n">
-        <v>37.01</v>
+        <v>34.81</v>
       </c>
       <c r="H231" s="1" t="n">
-        <v>47039</v>
+        <v>46768</v>
       </c>
     </row>
     <row r="232">
@@ -7858,16 +7846,16 @@
         <v>0</v>
       </c>
       <c r="E232" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F232" t="n">
-        <v>172.36</v>
+        <v>183.51</v>
       </c>
       <c r="G232" t="n">
-        <v>196.49</v>
+        <v>209.2</v>
       </c>
       <c r="H232" s="1" t="n">
-        <v>46871</v>
+        <v>46754</v>
       </c>
     </row>
     <row r="233">
@@ -7887,19 +7875,16 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>527</v>
+        <v>322</v>
       </c>
       <c r="E233" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F233" t="n">
-        <v>363.93</v>
+        <v>349.19</v>
       </c>
       <c r="G233" t="n">
-        <v>418.52</v>
-      </c>
-      <c r="H233" s="1" t="n">
-        <v>46783</v>
+        <v>401.57</v>
       </c>
     </row>
     <row r="234">
@@ -7919,19 +7904,19 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E234" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F234" t="n">
-        <v>237.59</v>
+        <v>223.08</v>
       </c>
       <c r="G234" t="n">
-        <v>275.6</v>
+        <v>258.77</v>
       </c>
       <c r="H234" s="1" t="n">
-        <v>46581</v>
+        <v>47186</v>
       </c>
     </row>
     <row r="235">
@@ -7951,19 +7936,19 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E235" t="n">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="F235" t="n">
-        <v>324.57</v>
+        <v>310.46</v>
       </c>
       <c r="G235" t="n">
-        <v>363.52</v>
+        <v>347.72</v>
       </c>
       <c r="H235" s="1" t="n">
-        <v>46338</v>
+        <v>46581</v>
       </c>
     </row>
     <row r="236">
@@ -7983,19 +7968,19 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>173</v>
+        <v>66</v>
       </c>
       <c r="E236" t="n">
-        <v>464</v>
+        <v>3</v>
       </c>
       <c r="F236" t="n">
-        <v>63.98</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="G236" t="n">
-        <v>76.78</v>
+        <v>80.41</v>
       </c>
       <c r="H236" s="1" t="n">
-        <v>47178</v>
+        <v>46399</v>
       </c>
     </row>
     <row r="237">
@@ -8015,19 +8000,19 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E237" t="n">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="F237" t="n">
-        <v>100.4</v>
+        <v>100.6</v>
       </c>
       <c r="G237" t="n">
-        <v>119.48</v>
+        <v>119.71</v>
       </c>
       <c r="H237" s="1" t="n">
-        <v>46770</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="238">
@@ -8047,19 +8032,19 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E238" t="n">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F238" t="n">
-        <v>384.96</v>
+        <v>367.53</v>
       </c>
       <c r="G238" t="n">
-        <v>431.16</v>
+        <v>411.63</v>
       </c>
       <c r="H238" s="1" t="n">
-        <v>47083</v>
+        <v>46557</v>
       </c>
     </row>
     <row r="239">
@@ -8079,19 +8064,19 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>42</v>
+        <v>142</v>
       </c>
       <c r="E239" t="n">
-        <v>3</v>
+        <v>442</v>
       </c>
       <c r="F239" t="n">
-        <v>1715.23</v>
+        <v>1599.08</v>
       </c>
       <c r="G239" t="n">
-        <v>1886.75</v>
+        <v>1758.99</v>
       </c>
       <c r="H239" s="1" t="n">
-        <v>46648</v>
+        <v>46843</v>
       </c>
     </row>
     <row r="240">
@@ -8111,19 +8096,19 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="E240" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F240" t="n">
-        <v>88.54000000000001</v>
+        <v>81</v>
       </c>
       <c r="G240" t="n">
-        <v>115.1</v>
+        <v>105.3</v>
       </c>
       <c r="H240" s="1" t="n">
-        <v>47047</v>
+        <v>47224</v>
       </c>
     </row>
     <row r="241">
@@ -8143,16 +8128,19 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>209</v>
+        <v>281</v>
       </c>
       <c r="E241" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="F241" t="n">
-        <v>62.6</v>
+        <v>58.92</v>
       </c>
       <c r="G241" t="n">
-        <v>84.51000000000001</v>
+        <v>79.54000000000001</v>
+      </c>
+      <c r="H241" s="1" t="n">
+        <v>46742</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/D_chain_multi_branch.xlsx
+++ b/sample_data/D_chain_multi_branch.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H241"/>
+  <dimension ref="A1:I241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,11 @@
           <t>Exp.</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -536,6 +541,11 @@
       <c r="H2" s="1" t="n">
         <v>47036</v>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -568,6 +578,11 @@
       <c r="H3" s="1" t="n">
         <v>46730</v>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -600,6 +615,11 @@
       <c r="H4" s="1" t="n">
         <v>46822</v>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -632,6 +652,11 @@
       <c r="H5" s="1" t="n">
         <v>47218</v>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -661,6 +686,11 @@
       <c r="G6" t="n">
         <v>35.49</v>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -693,6 +723,11 @@
       <c r="H7" s="1" t="n">
         <v>47193</v>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -725,6 +760,11 @@
       <c r="H8" s="1" t="n">
         <v>46987</v>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -757,6 +797,11 @@
       <c r="H9" s="1" t="n">
         <v>46678</v>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -789,6 +834,11 @@
       <c r="H10" s="1" t="n">
         <v>46874</v>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -821,6 +871,11 @@
       <c r="H11" s="1" t="n">
         <v>46616</v>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -853,6 +908,11 @@
       <c r="H12" s="1" t="n">
         <v>46319</v>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -885,6 +945,11 @@
       <c r="H13" s="1" t="n">
         <v>46761</v>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -917,6 +982,11 @@
       <c r="H14" s="1" t="n">
         <v>46675</v>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -949,6 +1019,11 @@
       <c r="H15" s="1" t="n">
         <v>46760</v>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -981,6 +1056,11 @@
       <c r="H16" s="1" t="n">
         <v>46394</v>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1013,6 +1093,11 @@
       <c r="H17" s="1" t="n">
         <v>47134</v>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1045,6 +1130,11 @@
       <c r="H18" s="1" t="n">
         <v>46829</v>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1077,6 +1167,11 @@
       <c r="H19" s="1" t="n">
         <v>46905</v>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1109,6 +1204,11 @@
       <c r="H20" s="1" t="n">
         <v>46606</v>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1141,6 +1241,11 @@
       <c r="H21" s="1" t="n">
         <v>46764</v>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1173,6 +1278,11 @@
       <c r="H22" s="1" t="n">
         <v>47130</v>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1205,6 +1315,11 @@
       <c r="H23" s="1" t="n">
         <v>47049</v>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1237,6 +1352,11 @@
       <c r="H24" s="1" t="n">
         <v>46789</v>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1269,6 +1389,11 @@
       <c r="H25" s="1" t="n">
         <v>46569</v>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1301,6 +1426,11 @@
       <c r="H26" s="1" t="n">
         <v>46394</v>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1333,6 +1463,11 @@
       <c r="H27" s="1" t="n">
         <v>46354</v>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1365,6 +1500,11 @@
       <c r="H28" s="1" t="n">
         <v>46314</v>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1397,6 +1537,11 @@
       <c r="H29" s="1" t="n">
         <v>46292</v>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1429,6 +1574,11 @@
       <c r="H30" s="1" t="n">
         <v>46670</v>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1461,6 +1611,11 @@
       <c r="H31" s="1" t="n">
         <v>46390</v>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1493,6 +1648,11 @@
       <c r="H32" s="1" t="n">
         <v>47163</v>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1525,6 +1685,11 @@
       <c r="H33" s="1" t="n">
         <v>46587</v>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1557,6 +1722,11 @@
       <c r="H34" s="1" t="n">
         <v>46389</v>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1589,6 +1759,11 @@
       <c r="H35" s="1" t="n">
         <v>46685</v>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1621,6 +1796,11 @@
       <c r="H36" s="1" t="n">
         <v>46681</v>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1653,6 +1833,11 @@
       <c r="H37" s="1" t="n">
         <v>46668</v>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1685,6 +1870,11 @@
       <c r="H38" s="1" t="n">
         <v>46557</v>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1714,6 +1904,11 @@
       <c r="G39" t="n">
         <v>77.18000000000001</v>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1746,6 +1941,11 @@
       <c r="H40" s="1" t="n">
         <v>46289</v>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1778,6 +1978,11 @@
       <c r="H41" s="1" t="n">
         <v>47195</v>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1810,6 +2015,11 @@
       <c r="H42" s="1" t="n">
         <v>47125</v>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1842,6 +2052,11 @@
       <c r="H43" s="1" t="n">
         <v>46999</v>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1874,6 +2089,11 @@
       <c r="H44" s="1" t="n">
         <v>46854</v>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1903,6 +2123,11 @@
       <c r="G45" t="n">
         <v>44.1</v>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1935,6 +2160,11 @@
       <c r="H46" s="1" t="n">
         <v>46967</v>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1967,6 +2197,11 @@
       <c r="H47" s="1" t="n">
         <v>46832</v>
       </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1999,6 +2234,11 @@
       <c r="H48" s="1" t="n">
         <v>46559</v>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2031,6 +2271,11 @@
       <c r="H49" s="1" t="n">
         <v>47214</v>
       </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2063,6 +2308,11 @@
       <c r="H50" s="1" t="n">
         <v>46294</v>
       </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2095,6 +2345,11 @@
       <c r="H51" s="1" t="n">
         <v>46589</v>
       </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2127,6 +2382,11 @@
       <c r="H52" s="1" t="n">
         <v>46353</v>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2159,6 +2419,11 @@
       <c r="H53" s="1" t="n">
         <v>46869</v>
       </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2191,6 +2456,11 @@
       <c r="H54" s="1" t="n">
         <v>46974</v>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2223,6 +2493,11 @@
       <c r="H55" s="1" t="n">
         <v>46391</v>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2255,6 +2530,11 @@
       <c r="H56" s="1" t="n">
         <v>46643</v>
       </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2284,6 +2564,11 @@
       <c r="G57" t="n">
         <v>741.09</v>
       </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2313,6 +2598,11 @@
       <c r="G58" t="n">
         <v>1081.22</v>
       </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2345,6 +2635,11 @@
       <c r="H59" s="1" t="n">
         <v>46957</v>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2377,6 +2672,11 @@
       <c r="H60" s="1" t="n">
         <v>46685</v>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2409,6 +2709,11 @@
       <c r="H61" s="1" t="n">
         <v>46557</v>
       </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2441,6 +2746,11 @@
       <c r="H62" s="1" t="n">
         <v>46749</v>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2473,6 +2783,11 @@
       <c r="H63" s="1" t="n">
         <v>46354</v>
       </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2505,6 +2820,11 @@
       <c r="H64" s="1" t="n">
         <v>46823</v>
       </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2537,6 +2857,11 @@
       <c r="H65" s="1" t="n">
         <v>47022</v>
       </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2569,6 +2894,11 @@
       <c r="H66" s="1" t="n">
         <v>47018</v>
       </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2601,6 +2931,11 @@
       <c r="H67" s="1" t="n">
         <v>46937</v>
       </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2633,6 +2968,11 @@
       <c r="H68" s="1" t="n">
         <v>47001</v>
       </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2662,6 +3002,11 @@
       <c r="G69" t="n">
         <v>33.36</v>
       </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2694,6 +3039,11 @@
       <c r="H70" s="1" t="n">
         <v>47017</v>
       </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2723,6 +3073,11 @@
       <c r="G71" t="n">
         <v>37.27</v>
       </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2755,6 +3110,11 @@
       <c r="H72" s="1" t="n">
         <v>46906</v>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2787,6 +3147,11 @@
       <c r="H73" s="1" t="n">
         <v>46594</v>
       </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2819,6 +3184,11 @@
       <c r="H74" s="1" t="n">
         <v>46800</v>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2851,6 +3221,11 @@
       <c r="H75" s="1" t="n">
         <v>46883</v>
       </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2883,6 +3258,11 @@
       <c r="H76" s="1" t="n">
         <v>47218</v>
       </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2915,6 +3295,11 @@
       <c r="H77" s="1" t="n">
         <v>46862</v>
       </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2947,6 +3332,11 @@
       <c r="H78" s="1" t="n">
         <v>46936</v>
       </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2979,6 +3369,11 @@
       <c r="H79" s="1" t="n">
         <v>47121</v>
       </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3011,6 +3406,11 @@
       <c r="H80" s="1" t="n">
         <v>46934</v>
       </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3043,6 +3443,11 @@
       <c r="H81" s="1" t="n">
         <v>46779</v>
       </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3075,6 +3480,11 @@
       <c r="H82" s="1" t="n">
         <v>46760</v>
       </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3107,6 +3517,11 @@
       <c r="H83" s="1" t="n">
         <v>46974</v>
       </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3139,6 +3554,11 @@
       <c r="H84" s="1" t="n">
         <v>46998</v>
       </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3171,6 +3591,11 @@
       <c r="H85" s="1" t="n">
         <v>46961</v>
       </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3203,6 +3628,11 @@
       <c r="H86" s="1" t="n">
         <v>47045</v>
       </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3235,6 +3665,11 @@
       <c r="H87" s="1" t="n">
         <v>46560</v>
       </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3267,6 +3702,11 @@
       <c r="H88" s="1" t="n">
         <v>47006</v>
       </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3299,6 +3739,11 @@
       <c r="H89" s="1" t="n">
         <v>46917</v>
       </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3331,6 +3776,11 @@
       <c r="H90" s="1" t="n">
         <v>46849</v>
       </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3363,6 +3813,11 @@
       <c r="H91" s="1" t="n">
         <v>46378</v>
       </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3395,6 +3850,11 @@
       <c r="H92" s="1" t="n">
         <v>46749</v>
       </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3427,6 +3887,11 @@
       <c r="H93" s="1" t="n">
         <v>47009</v>
       </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3459,6 +3924,11 @@
       <c r="H94" s="1" t="n">
         <v>46855</v>
       </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3491,6 +3961,11 @@
       <c r="H95" s="1" t="n">
         <v>47192</v>
       </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3523,6 +3998,11 @@
       <c r="H96" s="1" t="n">
         <v>47076</v>
       </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3555,6 +4035,11 @@
       <c r="H97" s="1" t="n">
         <v>46623</v>
       </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3587,6 +4072,11 @@
       <c r="H98" s="1" t="n">
         <v>46780</v>
       </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3619,6 +4109,11 @@
       <c r="H99" s="1" t="n">
         <v>46353</v>
       </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3651,6 +4146,11 @@
       <c r="H100" s="1" t="n">
         <v>46791</v>
       </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3680,6 +4180,11 @@
       <c r="G101" t="n">
         <v>260.39</v>
       </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3712,6 +4217,11 @@
       <c r="H102" s="1" t="n">
         <v>46533</v>
       </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3744,6 +4254,11 @@
       <c r="H103" s="1" t="n">
         <v>46992</v>
       </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3776,6 +4291,11 @@
       <c r="H104" s="1" t="n">
         <v>46357</v>
       </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3808,6 +4328,11 @@
       <c r="H105" s="1" t="n">
         <v>46928</v>
       </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3840,6 +4365,11 @@
       <c r="H106" s="1" t="n">
         <v>47190</v>
       </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3872,6 +4402,11 @@
       <c r="H107" s="1" t="n">
         <v>46691</v>
       </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3904,6 +4439,11 @@
       <c r="H108" s="1" t="n">
         <v>47126</v>
       </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3936,6 +4476,11 @@
       <c r="H109" s="1" t="n">
         <v>46307</v>
       </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3968,6 +4513,11 @@
       <c r="H110" s="1" t="n">
         <v>46381</v>
       </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4000,6 +4550,11 @@
       <c r="H111" s="1" t="n">
         <v>46848</v>
       </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4032,6 +4587,11 @@
       <c r="H112" s="1" t="n">
         <v>46944</v>
       </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4064,6 +4624,11 @@
       <c r="H113" s="1" t="n">
         <v>47131</v>
       </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4096,6 +4661,11 @@
       <c r="H114" s="1" t="n">
         <v>47211</v>
       </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4128,6 +4698,11 @@
       <c r="H115" s="1" t="n">
         <v>47156</v>
       </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4160,6 +4735,11 @@
       <c r="H116" s="1" t="n">
         <v>46302</v>
       </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4192,6 +4772,11 @@
       <c r="H117" s="1" t="n">
         <v>46920</v>
       </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4224,6 +4809,11 @@
       <c r="H118" s="1" t="n">
         <v>46863</v>
       </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4256,6 +4846,11 @@
       <c r="H119" s="1" t="n">
         <v>46710</v>
       </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4288,6 +4883,11 @@
       <c r="H120" s="1" t="n">
         <v>46891</v>
       </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4320,6 +4920,11 @@
       <c r="H121" s="1" t="n">
         <v>46623</v>
       </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4349,6 +4954,11 @@
       <c r="G122" t="n">
         <v>178.09</v>
       </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4381,6 +4991,11 @@
       <c r="H123" s="1" t="n">
         <v>46924</v>
       </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4413,6 +5028,11 @@
       <c r="H124" s="1" t="n">
         <v>47206</v>
       </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4445,6 +5065,11 @@
       <c r="H125" s="1" t="n">
         <v>46289</v>
       </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4477,6 +5102,11 @@
       <c r="H126" s="1" t="n">
         <v>47027</v>
       </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4509,6 +5139,11 @@
       <c r="H127" s="1" t="n">
         <v>46743</v>
       </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4541,6 +5176,11 @@
       <c r="H128" s="1" t="n">
         <v>46337</v>
       </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4573,6 +5213,11 @@
       <c r="H129" s="1" t="n">
         <v>46349</v>
       </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4605,6 +5250,11 @@
       <c r="H130" s="1" t="n">
         <v>46368</v>
       </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4637,6 +5287,11 @@
       <c r="H131" s="1" t="n">
         <v>46547</v>
       </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4669,6 +5324,11 @@
       <c r="H132" s="1" t="n">
         <v>46532</v>
       </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4701,6 +5361,11 @@
       <c r="H133" s="1" t="n">
         <v>46956</v>
       </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4733,6 +5398,11 @@
       <c r="H134" s="1" t="n">
         <v>47147</v>
       </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4765,6 +5435,11 @@
       <c r="H135" s="1" t="n">
         <v>46901</v>
       </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4797,6 +5472,11 @@
       <c r="H136" s="1" t="n">
         <v>46581</v>
       </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4829,6 +5509,11 @@
       <c r="H137" s="1" t="n">
         <v>46741</v>
       </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4861,6 +5546,11 @@
       <c r="H138" s="1" t="n">
         <v>46663</v>
       </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4893,6 +5583,11 @@
       <c r="H139" s="1" t="n">
         <v>47197</v>
       </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4925,6 +5620,11 @@
       <c r="H140" s="1" t="n">
         <v>46664</v>
       </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4957,6 +5657,11 @@
       <c r="H141" s="1" t="n">
         <v>46778</v>
       </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4989,6 +5694,11 @@
       <c r="H142" s="1" t="n">
         <v>46743</v>
       </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5021,6 +5731,11 @@
       <c r="H143" s="1" t="n">
         <v>46954</v>
       </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5053,6 +5768,11 @@
       <c r="H144" s="1" t="n">
         <v>47139</v>
       </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5085,6 +5805,11 @@
       <c r="H145" s="1" t="n">
         <v>47226</v>
       </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5117,6 +5842,11 @@
       <c r="H146" s="1" t="n">
         <v>46691</v>
       </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5149,6 +5879,11 @@
       <c r="H147" s="1" t="n">
         <v>46360</v>
       </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5181,6 +5916,11 @@
       <c r="H148" s="1" t="n">
         <v>46976</v>
       </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5213,6 +5953,11 @@
       <c r="H149" s="1" t="n">
         <v>46934</v>
       </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5245,6 +5990,11 @@
       <c r="H150" s="1" t="n">
         <v>46740</v>
       </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5274,6 +6024,11 @@
       <c r="G151" t="n">
         <v>36.85</v>
       </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5306,6 +6061,11 @@
       <c r="H152" s="1" t="n">
         <v>46592</v>
       </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5338,6 +6098,11 @@
       <c r="H153" s="1" t="n">
         <v>47080</v>
       </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5370,6 +6135,11 @@
       <c r="H154" s="1" t="n">
         <v>46953</v>
       </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5402,6 +6172,11 @@
       <c r="H155" s="1" t="n">
         <v>46896</v>
       </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5434,6 +6209,11 @@
       <c r="H156" s="1" t="n">
         <v>46860</v>
       </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5466,6 +6246,11 @@
       <c r="H157" s="1" t="n">
         <v>46626</v>
       </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5498,6 +6283,11 @@
       <c r="H158" s="1" t="n">
         <v>46581</v>
       </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5530,6 +6320,11 @@
       <c r="H159" s="1" t="n">
         <v>46563</v>
       </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5562,6 +6357,11 @@
       <c r="H160" s="1" t="n">
         <v>46382</v>
       </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5594,6 +6394,11 @@
       <c r="H161" s="1" t="n">
         <v>46587</v>
       </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5626,6 +6431,11 @@
       <c r="H162" s="1" t="n">
         <v>46683</v>
       </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5658,6 +6468,11 @@
       <c r="H163" s="1" t="n">
         <v>46999</v>
       </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5690,6 +6505,11 @@
       <c r="H164" s="1" t="n">
         <v>46646</v>
       </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5722,6 +6542,11 @@
       <c r="H165" s="1" t="n">
         <v>46360</v>
       </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5754,6 +6579,11 @@
       <c r="H166" s="1" t="n">
         <v>47171</v>
       </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5786,6 +6616,11 @@
       <c r="H167" s="1" t="n">
         <v>46915</v>
       </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5818,6 +6653,11 @@
       <c r="H168" s="1" t="n">
         <v>46793</v>
       </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5850,6 +6690,11 @@
       <c r="H169" s="1" t="n">
         <v>46762</v>
       </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5882,6 +6727,11 @@
       <c r="H170" s="1" t="n">
         <v>47011</v>
       </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5914,6 +6764,11 @@
       <c r="H171" s="1" t="n">
         <v>46996</v>
       </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5946,6 +6801,11 @@
       <c r="H172" s="1" t="n">
         <v>47148</v>
       </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5978,6 +6838,11 @@
       <c r="H173" s="1" t="n">
         <v>47030</v>
       </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6010,6 +6875,11 @@
       <c r="H174" s="1" t="n">
         <v>47141</v>
       </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6042,6 +6912,11 @@
       <c r="H175" s="1" t="n">
         <v>46786</v>
       </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6074,6 +6949,11 @@
       <c r="H176" s="1" t="n">
         <v>46984</v>
       </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6106,6 +6986,11 @@
       <c r="H177" s="1" t="n">
         <v>47060</v>
       </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6138,6 +7023,11 @@
       <c r="H178" s="1" t="n">
         <v>46679</v>
       </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6170,6 +7060,11 @@
       <c r="H179" s="1" t="n">
         <v>46292</v>
       </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6202,6 +7097,11 @@
       <c r="H180" s="1" t="n">
         <v>46356</v>
       </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6234,6 +7134,11 @@
       <c r="H181" s="1" t="n">
         <v>46900</v>
       </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6266,6 +7171,11 @@
       <c r="H182" s="1" t="n">
         <v>47193</v>
       </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6298,6 +7208,11 @@
       <c r="H183" s="1" t="n">
         <v>46344</v>
       </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6330,6 +7245,11 @@
       <c r="H184" s="1" t="n">
         <v>47078</v>
       </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6362,6 +7282,11 @@
       <c r="H185" s="1" t="n">
         <v>46656</v>
       </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6394,6 +7319,11 @@
       <c r="H186" s="1" t="n">
         <v>46724</v>
       </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6426,6 +7356,11 @@
       <c r="H187" s="1" t="n">
         <v>47214</v>
       </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6458,6 +7393,11 @@
       <c r="H188" s="1" t="n">
         <v>46944</v>
       </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6490,6 +7430,11 @@
       <c r="H189" s="1" t="n">
         <v>47107</v>
       </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6522,6 +7467,11 @@
       <c r="H190" s="1" t="n">
         <v>46832</v>
       </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6554,6 +7504,11 @@
       <c r="H191" s="1" t="n">
         <v>46760</v>
       </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6586,6 +7541,11 @@
       <c r="H192" s="1" t="n">
         <v>46380</v>
       </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6618,6 +7578,11 @@
       <c r="H193" s="1" t="n">
         <v>46629</v>
       </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6650,6 +7615,11 @@
       <c r="H194" s="1" t="n">
         <v>46389</v>
       </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6682,6 +7652,11 @@
       <c r="H195" s="1" t="n">
         <v>46307</v>
       </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6714,6 +7689,11 @@
       <c r="H196" s="1" t="n">
         <v>46678</v>
       </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6746,6 +7726,11 @@
       <c r="H197" s="1" t="n">
         <v>46344</v>
       </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6778,6 +7763,11 @@
       <c r="H198" s="1" t="n">
         <v>46550</v>
       </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6810,6 +7800,11 @@
       <c r="H199" s="1" t="n">
         <v>46538</v>
       </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6842,6 +7837,11 @@
       <c r="H200" s="1" t="n">
         <v>46341</v>
       </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6874,6 +7874,11 @@
       <c r="H201" s="1" t="n">
         <v>46780</v>
       </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6906,6 +7911,11 @@
       <c r="H202" s="1" t="n">
         <v>46970</v>
       </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6938,6 +7948,11 @@
       <c r="H203" s="1" t="n">
         <v>46557</v>
       </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6970,6 +7985,11 @@
       <c r="H204" s="1" t="n">
         <v>47191</v>
       </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7002,6 +8022,11 @@
       <c r="H205" s="1" t="n">
         <v>46531</v>
       </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7034,6 +8059,11 @@
       <c r="H206" s="1" t="n">
         <v>46918</v>
       </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7066,6 +8096,11 @@
       <c r="H207" s="1" t="n">
         <v>46868</v>
       </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7098,6 +8133,11 @@
       <c r="H208" s="1" t="n">
         <v>46359</v>
       </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7130,6 +8170,11 @@
       <c r="H209" s="1" t="n">
         <v>46784</v>
       </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7162,6 +8207,11 @@
       <c r="H210" s="1" t="n">
         <v>46673</v>
       </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7194,6 +8244,11 @@
       <c r="H211" s="1" t="n">
         <v>46835</v>
       </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7226,6 +8281,11 @@
       <c r="H212" s="1" t="n">
         <v>46659</v>
       </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7258,6 +8318,11 @@
       <c r="H213" s="1" t="n">
         <v>46878</v>
       </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7290,6 +8355,11 @@
       <c r="H214" s="1" t="n">
         <v>46613</v>
       </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7322,6 +8392,11 @@
       <c r="H215" s="1" t="n">
         <v>46584</v>
       </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7354,6 +8429,11 @@
       <c r="H216" s="1" t="n">
         <v>47199</v>
       </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7386,6 +8466,11 @@
       <c r="H217" s="1" t="n">
         <v>46919</v>
       </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7418,6 +8503,11 @@
       <c r="H218" s="1" t="n">
         <v>46766</v>
       </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7447,6 +8537,11 @@
       <c r="G219" t="n">
         <v>606.84</v>
       </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7476,6 +8571,11 @@
       <c r="G220" t="n">
         <v>829.14</v>
       </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7508,6 +8608,11 @@
       <c r="H221" s="1" t="n">
         <v>46972</v>
       </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7540,6 +8645,11 @@
       <c r="H222" s="1" t="n">
         <v>47040</v>
       </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7572,6 +8682,11 @@
       <c r="H223" s="1" t="n">
         <v>46782</v>
       </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7604,6 +8719,11 @@
       <c r="H224" s="1" t="n">
         <v>47038</v>
       </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7636,6 +8756,11 @@
       <c r="H225" s="1" t="n">
         <v>46972</v>
       </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7665,6 +8790,11 @@
       <c r="G226" t="n">
         <v>170.75</v>
       </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7697,6 +8827,11 @@
       <c r="H227" s="1" t="n">
         <v>46896</v>
       </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7729,6 +8864,11 @@
       <c r="H228" s="1" t="n">
         <v>46800</v>
       </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7761,6 +8901,11 @@
       <c r="H229" s="1" t="n">
         <v>46883</v>
       </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7793,6 +8938,11 @@
       <c r="H230" s="1" t="n">
         <v>47149</v>
       </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7825,6 +8975,11 @@
       <c r="H231" s="1" t="n">
         <v>46768</v>
       </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7857,6 +9012,11 @@
       <c r="H232" s="1" t="n">
         <v>46754</v>
       </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7886,6 +9046,11 @@
       <c r="G233" t="n">
         <v>401.57</v>
       </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7918,6 +9083,11 @@
       <c r="H234" s="1" t="n">
         <v>47186</v>
       </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7950,6 +9120,11 @@
       <c r="H235" s="1" t="n">
         <v>46581</v>
       </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7982,6 +9157,11 @@
       <c r="H236" s="1" t="n">
         <v>46399</v>
       </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8014,6 +9194,11 @@
       <c r="H237" s="1" t="n">
         <v>46304</v>
       </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8046,6 +9231,11 @@
       <c r="H238" s="1" t="n">
         <v>46557</v>
       </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8078,6 +9268,11 @@
       <c r="H239" s="1" t="n">
         <v>46843</v>
       </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8110,6 +9305,11 @@
       <c r="H240" s="1" t="n">
         <v>47224</v>
       </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8141,6 +9341,11 @@
       </c>
       <c r="H241" s="1" t="n">
         <v>46742</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
       </c>
     </row>
   </sheetData>
